--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY273"/>
+  <dimension ref="A1:AY274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31637,6 +31637,141 @@
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>122005407</v>
+      </c>
+      <c r="B274" t="n">
+        <v>82713</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>791</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Barrtryffel</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Hydnotrya michaelis</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>(E.Fisch.) Trappe</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Linvallen, 30 m nedströms bron över Livsäterån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>369515</v>
+      </c>
+      <c r="R274" t="n">
+        <v>6938184</v>
+      </c>
+      <c r="S274" t="n">
+        <v>50</v>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>1987-09-02</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>1987-09-02</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>Leg. L.E.Kers</t>
+        </is>
+      </c>
+      <c r="AD274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF274" t="inlineStr"/>
+      <c r="AG274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>Bäckravinslänt, nordsluttningen, ca 30 m nerströms bron. Granskog. Grupp av gamla granar. Under brrförna ovan på starkt multnad förna. Här ock Tuber.</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>F-120874</t>
+        </is>
+      </c>
+      <c r="AT274" t="inlineStr"/>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>Mikael Jeppson</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Mikael Jeppson</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>Via Mikael Jeppson</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>Svenska tryffelprojektet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31642,7 +31642,7 @@
         <v>122005407</v>
       </c>
       <c r="B274" t="n">
-        <v>82713</v>
+        <v>82715</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31642,7 +31642,7 @@
         <v>122005407</v>
       </c>
       <c r="B274" t="n">
-        <v>82715</v>
+        <v>82716</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31642,7 +31642,7 @@
         <v>122005407</v>
       </c>
       <c r="B274" t="n">
-        <v>82716</v>
+        <v>82725</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31642,7 +31642,7 @@
         <v>122005407</v>
       </c>
       <c r="B274" t="n">
-        <v>82731</v>
+        <v>82732</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31642,7 +31642,7 @@
         <v>122005407</v>
       </c>
       <c r="B274" t="n">
-        <v>82732</v>
+        <v>82737</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124625773</v>
+        <v>124624504</v>
       </c>
       <c r="B274" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31677,34 +31677,39 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368933</v>
+        <v>368934</v>
       </c>
       <c r="R274" t="n">
-        <v>6938257</v>
+        <v>6938300</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31763,10 +31768,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124621836</v>
+        <v>124625988</v>
       </c>
       <c r="B275" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31775,41 +31780,41 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>368827</v>
+        <v>368879</v>
       </c>
       <c r="R275" t="n">
-        <v>6937946</v>
+        <v>6938246</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31865,10 +31870,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124625988</v>
+        <v>124624537</v>
       </c>
       <c r="B276" t="n">
-        <v>91700</v>
+        <v>91030</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31877,41 +31882,41 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368879</v>
+        <v>368960</v>
       </c>
       <c r="R276" t="n">
-        <v>6938246</v>
+        <v>6938297</v>
       </c>
       <c r="S276" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -32074,10 +32079,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124624537</v>
+        <v>124624109</v>
       </c>
       <c r="B278" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32090,34 +32095,34 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368960</v>
+        <v>368931</v>
       </c>
       <c r="R278" t="n">
-        <v>6938297</v>
+        <v>6938267</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32176,10 +32181,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124625410</v>
+        <v>124621864</v>
       </c>
       <c r="B279" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32192,37 +32197,37 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>369017</v>
+        <v>368827</v>
       </c>
       <c r="R279" t="n">
-        <v>6938332</v>
+        <v>6937946</v>
       </c>
       <c r="S279" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32278,10 +32283,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124624504</v>
+        <v>124625410</v>
       </c>
       <c r="B280" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -32294,42 +32299,37 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>368934</v>
+        <v>369017</v>
       </c>
       <c r="R280" t="n">
-        <v>6938300</v>
+        <v>6938332</v>
       </c>
       <c r="S280" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32385,10 +32385,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124621864</v>
+        <v>124625773</v>
       </c>
       <c r="B281" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32401,21 +32401,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -32425,10 +32425,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368827</v>
+        <v>368933</v>
       </c>
       <c r="R281" t="n">
-        <v>6937946</v>
+        <v>6938257</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -32487,10 +32487,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124624109</v>
+        <v>124621836</v>
       </c>
       <c r="B282" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32503,34 +32503,34 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368931</v>
+        <v>368827</v>
       </c>
       <c r="R282" t="n">
-        <v>6938267</v>
+        <v>6937946</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124624504</v>
+        <v>124625773</v>
       </c>
       <c r="B274" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31677,39 +31677,34 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P274" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368934</v>
+        <v>368933</v>
       </c>
       <c r="R274" t="n">
-        <v>6938300</v>
+        <v>6938257</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31972,10 +31967,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124622472</v>
+        <v>124625410</v>
       </c>
       <c r="B277" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31988,42 +31983,37 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>368802</v>
+        <v>369017</v>
       </c>
       <c r="R277" t="n">
-        <v>6938048</v>
+        <v>6938332</v>
       </c>
       <c r="S277" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -32181,10 +32171,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124621864</v>
+        <v>124622472</v>
       </c>
       <c r="B279" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32197,37 +32187,42 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P279" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>368827</v>
+        <v>368802</v>
       </c>
       <c r="R279" t="n">
-        <v>6937946</v>
+        <v>6938048</v>
       </c>
       <c r="S279" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32283,10 +32278,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124625410</v>
+        <v>124621864</v>
       </c>
       <c r="B280" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -32299,37 +32294,37 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>369017</v>
+        <v>368827</v>
       </c>
       <c r="R280" t="n">
-        <v>6938332</v>
+        <v>6937946</v>
       </c>
       <c r="S280" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32385,10 +32380,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124625773</v>
+        <v>124624504</v>
       </c>
       <c r="B281" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32401,34 +32396,39 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P281" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368933</v>
+        <v>368934</v>
       </c>
       <c r="R281" t="n">
-        <v>6938257</v>
+        <v>6938300</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124625773</v>
+        <v>124624504</v>
       </c>
       <c r="B274" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31677,34 +31677,39 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368933</v>
+        <v>368934</v>
       </c>
       <c r="R274" t="n">
-        <v>6938257</v>
+        <v>6938300</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31763,10 +31768,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124625988</v>
+        <v>124625410</v>
       </c>
       <c r="B275" t="n">
-        <v>91700</v>
+        <v>91030</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31775,25 +31780,25 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -31803,10 +31808,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>368879</v>
+        <v>369017</v>
       </c>
       <c r="R275" t="n">
-        <v>6938246</v>
+        <v>6938332</v>
       </c>
       <c r="S275" t="n">
         <v>25</v>
@@ -31865,7 +31870,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124624537</v>
+        <v>124625773</v>
       </c>
       <c r="B276" t="n">
         <v>91030</v>
@@ -31905,10 +31910,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368960</v>
+        <v>368933</v>
       </c>
       <c r="R276" t="n">
-        <v>6938297</v>
+        <v>6938257</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31967,10 +31972,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124625410</v>
+        <v>124625988</v>
       </c>
       <c r="B277" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31979,25 +31984,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -32007,10 +32012,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>369017</v>
+        <v>368879</v>
       </c>
       <c r="R277" t="n">
-        <v>6938332</v>
+        <v>6938246</v>
       </c>
       <c r="S277" t="n">
         <v>25</v>
@@ -32069,10 +32074,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124624109</v>
+        <v>124624537</v>
       </c>
       <c r="B278" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32085,34 +32090,34 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368931</v>
+        <v>368960</v>
       </c>
       <c r="R278" t="n">
-        <v>6938267</v>
+        <v>6938297</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32171,10 +32176,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124622472</v>
+        <v>124621836</v>
       </c>
       <c r="B279" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32187,42 +32192,37 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P279" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>368802</v>
+        <v>368827</v>
       </c>
       <c r="R279" t="n">
-        <v>6938048</v>
+        <v>6937946</v>
       </c>
       <c r="S279" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32278,10 +32278,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124621864</v>
+        <v>124624109</v>
       </c>
       <c r="B280" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -32294,34 +32294,34 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>368827</v>
+        <v>368931</v>
       </c>
       <c r="R280" t="n">
-        <v>6937946</v>
+        <v>6938267</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -32380,10 +32380,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124624504</v>
+        <v>124621864</v>
       </c>
       <c r="B281" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32396,39 +32396,34 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P281" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368934</v>
+        <v>368827</v>
       </c>
       <c r="R281" t="n">
-        <v>6938300</v>
+        <v>6937946</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -32487,10 +32482,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124621836</v>
+        <v>124622472</v>
       </c>
       <c r="B282" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32503,37 +32498,42 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P282" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368827</v>
+        <v>368802</v>
       </c>
       <c r="R282" t="n">
-        <v>6937946</v>
+        <v>6938048</v>
       </c>
       <c r="S282" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124624504</v>
+        <v>124625988</v>
       </c>
       <c r="B274" t="n">
-        <v>57513</v>
+        <v>91700</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31673,46 +31673,41 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368934</v>
+        <v>368879</v>
       </c>
       <c r="R274" t="n">
-        <v>6938300</v>
+        <v>6938246</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -31768,7 +31763,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124625410</v>
+        <v>124624537</v>
       </c>
       <c r="B275" t="n">
         <v>91030</v>
@@ -31804,17 +31799,17 @@
       <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>369017</v>
+        <v>368960</v>
       </c>
       <c r="R275" t="n">
-        <v>6938332</v>
+        <v>6938297</v>
       </c>
       <c r="S275" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31870,10 +31865,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124625773</v>
+        <v>124624504</v>
       </c>
       <c r="B276" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31886,34 +31881,39 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P276" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368933</v>
+        <v>368934</v>
       </c>
       <c r="R276" t="n">
-        <v>6938257</v>
+        <v>6938300</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31972,10 +31972,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124625988</v>
+        <v>124621864</v>
       </c>
       <c r="B277" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31984,41 +31984,41 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>368879</v>
+        <v>368827</v>
       </c>
       <c r="R277" t="n">
-        <v>6938246</v>
+        <v>6937946</v>
       </c>
       <c r="S277" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124624537</v>
+        <v>124621836</v>
       </c>
       <c r="B278" t="n">
         <v>91030</v>
@@ -32114,10 +32114,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368960</v>
+        <v>368827</v>
       </c>
       <c r="R278" t="n">
-        <v>6938297</v>
+        <v>6937946</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32176,7 +32176,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124621836</v>
+        <v>124625410</v>
       </c>
       <c r="B279" t="n">
         <v>91030</v>
@@ -32212,17 +32212,17 @@
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>368827</v>
+        <v>369017</v>
       </c>
       <c r="R279" t="n">
-        <v>6937946</v>
+        <v>6938332</v>
       </c>
       <c r="S279" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32380,10 +32380,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124621864</v>
+        <v>124622472</v>
       </c>
       <c r="B281" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32396,37 +32396,42 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P281" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368827</v>
+        <v>368802</v>
       </c>
       <c r="R281" t="n">
-        <v>6937946</v>
+        <v>6938048</v>
       </c>
       <c r="S281" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -32482,10 +32487,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124622472</v>
+        <v>124625773</v>
       </c>
       <c r="B282" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32498,42 +32503,37 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P282" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368802</v>
+        <v>368933</v>
       </c>
       <c r="R282" t="n">
-        <v>6938048</v>
+        <v>6938257</v>
       </c>
       <c r="S282" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124625988</v>
+        <v>124625773</v>
       </c>
       <c r="B274" t="n">
-        <v>91700</v>
+        <v>91030</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31673,41 +31673,41 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368879</v>
+        <v>368933</v>
       </c>
       <c r="R274" t="n">
-        <v>6938246</v>
+        <v>6938257</v>
       </c>
       <c r="S274" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124624537</v>
+        <v>124621836</v>
       </c>
       <c r="B275" t="n">
         <v>91030</v>
@@ -31803,10 +31803,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>368960</v>
+        <v>368827</v>
       </c>
       <c r="R275" t="n">
-        <v>6938297</v>
+        <v>6937946</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -31865,10 +31865,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124624504</v>
+        <v>124625988</v>
       </c>
       <c r="B276" t="n">
-        <v>57513</v>
+        <v>91700</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31877,46 +31877,41 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368934</v>
+        <v>368879</v>
       </c>
       <c r="R276" t="n">
-        <v>6938300</v>
+        <v>6938246</v>
       </c>
       <c r="S276" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -31972,10 +31967,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124621864</v>
+        <v>124625410</v>
       </c>
       <c r="B277" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31988,37 +31983,37 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>368827</v>
+        <v>369017</v>
       </c>
       <c r="R277" t="n">
-        <v>6937946</v>
+        <v>6938332</v>
       </c>
       <c r="S277" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -32074,10 +32069,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124621836</v>
+        <v>124622472</v>
       </c>
       <c r="B278" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32090,37 +32085,42 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368827</v>
+        <v>368802</v>
       </c>
       <c r="R278" t="n">
-        <v>6937946</v>
+        <v>6938048</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -32176,10 +32176,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124625410</v>
+        <v>124621864</v>
       </c>
       <c r="B279" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32192,37 +32192,37 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>369017</v>
+        <v>368827</v>
       </c>
       <c r="R279" t="n">
-        <v>6938332</v>
+        <v>6937946</v>
       </c>
       <c r="S279" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32380,10 +32380,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124622472</v>
+        <v>124624537</v>
       </c>
       <c r="B281" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32396,42 +32396,37 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P281" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368802</v>
+        <v>368960</v>
       </c>
       <c r="R281" t="n">
-        <v>6938048</v>
+        <v>6938297</v>
       </c>
       <c r="S281" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -32487,10 +32482,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124625773</v>
+        <v>124624504</v>
       </c>
       <c r="B282" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32503,34 +32498,39 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P282" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368933</v>
+        <v>368934</v>
       </c>
       <c r="R282" t="n">
-        <v>6938257</v>
+        <v>6938300</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31763,10 +31763,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124621836</v>
+        <v>124621864</v>
       </c>
       <c r="B275" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31779,21 +31779,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -31865,10 +31865,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124625988</v>
+        <v>124622472</v>
       </c>
       <c r="B276" t="n">
-        <v>91700</v>
+        <v>57513</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31877,41 +31877,46 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368879</v>
+        <v>368802</v>
       </c>
       <c r="R276" t="n">
-        <v>6938246</v>
+        <v>6938048</v>
       </c>
       <c r="S276" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -31967,10 +31972,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124625410</v>
+        <v>124624109</v>
       </c>
       <c r="B277" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31983,21 +31988,21 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -32007,13 +32012,13 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>369017</v>
+        <v>368931</v>
       </c>
       <c r="R277" t="n">
-        <v>6938332</v>
+        <v>6938267</v>
       </c>
       <c r="S277" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -32069,10 +32074,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124622472</v>
+        <v>124624537</v>
       </c>
       <c r="B278" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32085,42 +32090,37 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368802</v>
+        <v>368960</v>
       </c>
       <c r="R278" t="n">
-        <v>6938048</v>
+        <v>6938297</v>
       </c>
       <c r="S278" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -32176,10 +32176,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124621864</v>
+        <v>124621836</v>
       </c>
       <c r="B279" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32192,21 +32192,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -32278,10 +32278,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124624109</v>
+        <v>124624504</v>
       </c>
       <c r="B280" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -32294,34 +32294,39 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>368931</v>
+        <v>368934</v>
       </c>
       <c r="R280" t="n">
-        <v>6938267</v>
+        <v>6938300</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -32380,10 +32385,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124624537</v>
+        <v>124625988</v>
       </c>
       <c r="B281" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32392,41 +32397,41 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368960</v>
+        <v>368879</v>
       </c>
       <c r="R281" t="n">
-        <v>6938297</v>
+        <v>6938246</v>
       </c>
       <c r="S281" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -32482,10 +32487,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124624504</v>
+        <v>124625410</v>
       </c>
       <c r="B282" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32498,42 +32503,37 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368934</v>
+        <v>369017</v>
       </c>
       <c r="R282" t="n">
-        <v>6938300</v>
+        <v>6938332</v>
       </c>
       <c r="S282" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124625773</v>
+        <v>124624109</v>
       </c>
       <c r="B274" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31677,34 +31677,34 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368933</v>
+        <v>368931</v>
       </c>
       <c r="R274" t="n">
-        <v>6938257</v>
+        <v>6938267</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31763,10 +31763,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124621864</v>
+        <v>124621836</v>
       </c>
       <c r="B275" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31779,21 +31779,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -31865,10 +31865,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124622472</v>
+        <v>124625773</v>
       </c>
       <c r="B276" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31881,42 +31881,37 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P276" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368802</v>
+        <v>368933</v>
       </c>
       <c r="R276" t="n">
-        <v>6938048</v>
+        <v>6938257</v>
       </c>
       <c r="S276" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -31972,10 +31967,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124624109</v>
+        <v>124624537</v>
       </c>
       <c r="B277" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31988,34 +31983,34 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>368931</v>
+        <v>368960</v>
       </c>
       <c r="R277" t="n">
-        <v>6938267</v>
+        <v>6938297</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -32074,10 +32069,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124624537</v>
+        <v>124621864</v>
       </c>
       <c r="B278" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32090,21 +32085,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -32114,10 +32109,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368960</v>
+        <v>368827</v>
       </c>
       <c r="R278" t="n">
-        <v>6938297</v>
+        <v>6937946</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32176,10 +32171,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124621836</v>
+        <v>124624504</v>
       </c>
       <c r="B279" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32192,34 +32187,39 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P279" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>368827</v>
+        <v>368934</v>
       </c>
       <c r="R279" t="n">
-        <v>6937946</v>
+        <v>6938300</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -32278,10 +32278,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124624504</v>
+        <v>124625410</v>
       </c>
       <c r="B280" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -32294,42 +32294,37 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>368934</v>
+        <v>369017</v>
       </c>
       <c r="R280" t="n">
-        <v>6938300</v>
+        <v>6938332</v>
       </c>
       <c r="S280" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32385,10 +32380,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124625988</v>
+        <v>124622472</v>
       </c>
       <c r="B281" t="n">
-        <v>91700</v>
+        <v>57513</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32397,41 +32392,46 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368879</v>
+        <v>368802</v>
       </c>
       <c r="R281" t="n">
-        <v>6938246</v>
+        <v>6938048</v>
       </c>
       <c r="S281" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -32487,10 +32487,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124625410</v>
+        <v>124625988</v>
       </c>
       <c r="B282" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32499,25 +32499,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -32527,10 +32527,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>369017</v>
+        <v>368879</v>
       </c>
       <c r="R282" t="n">
-        <v>6938332</v>
+        <v>6938246</v>
       </c>
       <c r="S282" t="n">
         <v>25</v>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31865,10 +31865,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124625773</v>
+        <v>124624504</v>
       </c>
       <c r="B276" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31881,34 +31881,39 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P276" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368933</v>
+        <v>368934</v>
       </c>
       <c r="R276" t="n">
-        <v>6938257</v>
+        <v>6938300</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31967,7 +31972,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124624537</v>
+        <v>124625410</v>
       </c>
       <c r="B277" t="n">
         <v>91030</v>
@@ -32003,17 +32008,17 @@
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>368960</v>
+        <v>369017</v>
       </c>
       <c r="R277" t="n">
-        <v>6938297</v>
+        <v>6938332</v>
       </c>
       <c r="S277" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -32069,10 +32074,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124621864</v>
+        <v>124622472</v>
       </c>
       <c r="B278" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32085,37 +32090,42 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368827</v>
+        <v>368802</v>
       </c>
       <c r="R278" t="n">
-        <v>6937946</v>
+        <v>6938048</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -32171,10 +32181,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124624504</v>
+        <v>124625988</v>
       </c>
       <c r="B279" t="n">
-        <v>57513</v>
+        <v>91700</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32183,46 +32193,41 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>368934</v>
+        <v>368879</v>
       </c>
       <c r="R279" t="n">
-        <v>6938300</v>
+        <v>6938246</v>
       </c>
       <c r="S279" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32278,7 +32283,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124625410</v>
+        <v>124625773</v>
       </c>
       <c r="B280" t="n">
         <v>91030</v>
@@ -32314,17 +32319,17 @@
       <c r="I280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>369017</v>
+        <v>368933</v>
       </c>
       <c r="R280" t="n">
-        <v>6938332</v>
+        <v>6938257</v>
       </c>
       <c r="S280" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32380,10 +32385,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124622472</v>
+        <v>124621864</v>
       </c>
       <c r="B281" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32396,42 +32401,37 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P281" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368802</v>
+        <v>368827</v>
       </c>
       <c r="R281" t="n">
-        <v>6938048</v>
+        <v>6937946</v>
       </c>
       <c r="S281" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -32487,10 +32487,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124625988</v>
+        <v>124624537</v>
       </c>
       <c r="B282" t="n">
-        <v>91700</v>
+        <v>91030</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32499,41 +32499,41 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368879</v>
+        <v>368960</v>
       </c>
       <c r="R282" t="n">
-        <v>6938246</v>
+        <v>6938297</v>
       </c>
       <c r="S282" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31763,10 +31763,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124621836</v>
+        <v>124622472</v>
       </c>
       <c r="B275" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31779,37 +31779,42 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P275" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>368827</v>
+        <v>368802</v>
       </c>
       <c r="R275" t="n">
-        <v>6937946</v>
+        <v>6938048</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31865,10 +31870,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124624504</v>
+        <v>124625410</v>
       </c>
       <c r="B276" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31881,42 +31886,37 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368934</v>
+        <v>369017</v>
       </c>
       <c r="R276" t="n">
-        <v>6938300</v>
+        <v>6938332</v>
       </c>
       <c r="S276" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -31972,10 +31972,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124625410</v>
+        <v>124624504</v>
       </c>
       <c r="B277" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31988,37 +31988,42 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>369017</v>
+        <v>368934</v>
       </c>
       <c r="R277" t="n">
-        <v>6938332</v>
+        <v>6938300</v>
       </c>
       <c r="S277" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -32074,10 +32079,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124622472</v>
+        <v>124624537</v>
       </c>
       <c r="B278" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32090,42 +32095,37 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368802</v>
+        <v>368960</v>
       </c>
       <c r="R278" t="n">
-        <v>6938048</v>
+        <v>6938297</v>
       </c>
       <c r="S278" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -32181,10 +32181,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124625988</v>
+        <v>124625773</v>
       </c>
       <c r="B279" t="n">
-        <v>91700</v>
+        <v>91030</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32193,41 +32193,41 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>368879</v>
+        <v>368933</v>
       </c>
       <c r="R279" t="n">
-        <v>6938246</v>
+        <v>6938257</v>
       </c>
       <c r="S279" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32283,10 +32283,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124625773</v>
+        <v>124621864</v>
       </c>
       <c r="B280" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -32299,21 +32299,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -32323,10 +32323,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>368933</v>
+        <v>368827</v>
       </c>
       <c r="R280" t="n">
-        <v>6938257</v>
+        <v>6937946</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -32385,10 +32385,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124621864</v>
+        <v>124621836</v>
       </c>
       <c r="B281" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32401,21 +32401,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -32487,10 +32487,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124624537</v>
+        <v>124625988</v>
       </c>
       <c r="B282" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32499,41 +32499,41 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368960</v>
+        <v>368879</v>
       </c>
       <c r="R282" t="n">
-        <v>6938297</v>
+        <v>6938246</v>
       </c>
       <c r="S282" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124624109</v>
+        <v>124624537</v>
       </c>
       <c r="B274" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31677,34 +31677,34 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368931</v>
+        <v>368960</v>
       </c>
       <c r="R274" t="n">
-        <v>6938267</v>
+        <v>6938297</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31763,10 +31763,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124622472</v>
+        <v>124625773</v>
       </c>
       <c r="B275" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31779,42 +31779,37 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P275" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>368802</v>
+        <v>368933</v>
       </c>
       <c r="R275" t="n">
-        <v>6938048</v>
+        <v>6938257</v>
       </c>
       <c r="S275" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31870,10 +31865,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124625410</v>
+        <v>124622472</v>
       </c>
       <c r="B276" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31886,37 +31881,42 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>369017</v>
+        <v>368802</v>
       </c>
       <c r="R276" t="n">
-        <v>6938332</v>
+        <v>6938048</v>
       </c>
       <c r="S276" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -32079,10 +32079,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124624537</v>
+        <v>124621864</v>
       </c>
       <c r="B278" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32095,21 +32095,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -32119,10 +32119,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368960</v>
+        <v>368827</v>
       </c>
       <c r="R278" t="n">
-        <v>6938297</v>
+        <v>6937946</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32181,7 +32181,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124625773</v>
+        <v>124625410</v>
       </c>
       <c r="B279" t="n">
         <v>91030</v>
@@ -32217,17 +32217,17 @@
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>368933</v>
+        <v>369017</v>
       </c>
       <c r="R279" t="n">
-        <v>6938257</v>
+        <v>6938332</v>
       </c>
       <c r="S279" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32283,10 +32283,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124621864</v>
+        <v>124621836</v>
       </c>
       <c r="B280" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -32299,21 +32299,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -32385,10 +32385,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124621836</v>
+        <v>124625988</v>
       </c>
       <c r="B281" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32397,41 +32397,41 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368827</v>
+        <v>368879</v>
       </c>
       <c r="R281" t="n">
-        <v>6937946</v>
+        <v>6938246</v>
       </c>
       <c r="S281" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -32487,10 +32487,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124625988</v>
+        <v>124624109</v>
       </c>
       <c r="B282" t="n">
-        <v>91700</v>
+        <v>91008</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32499,25 +32499,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -32527,13 +32527,13 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368879</v>
+        <v>368931</v>
       </c>
       <c r="R282" t="n">
-        <v>6938246</v>
+        <v>6938267</v>
       </c>
       <c r="S282" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31763,10 +31763,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124625773</v>
+        <v>124625988</v>
       </c>
       <c r="B275" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31775,41 +31775,41 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>368933</v>
+        <v>368879</v>
       </c>
       <c r="R275" t="n">
-        <v>6938257</v>
+        <v>6938246</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31972,10 +31972,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124624504</v>
+        <v>124625773</v>
       </c>
       <c r="B277" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31988,39 +31988,34 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P277" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>368934</v>
+        <v>368933</v>
       </c>
       <c r="R277" t="n">
-        <v>6938300</v>
+        <v>6938257</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -32181,10 +32176,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124625410</v>
+        <v>124624504</v>
       </c>
       <c r="B279" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32197,37 +32192,42 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>369017</v>
+        <v>368934</v>
       </c>
       <c r="R279" t="n">
-        <v>6938332</v>
+        <v>6938300</v>
       </c>
       <c r="S279" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124621836</v>
+        <v>124625410</v>
       </c>
       <c r="B280" t="n">
         <v>91030</v>
@@ -32319,17 +32319,17 @@
       <c r="I280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>368827</v>
+        <v>369017</v>
       </c>
       <c r="R280" t="n">
-        <v>6937946</v>
+        <v>6938332</v>
       </c>
       <c r="S280" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32385,10 +32385,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124625988</v>
+        <v>124621836</v>
       </c>
       <c r="B281" t="n">
-        <v>91700</v>
+        <v>91030</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32397,41 +32397,41 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368879</v>
+        <v>368827</v>
       </c>
       <c r="R281" t="n">
-        <v>6938246</v>
+        <v>6937946</v>
       </c>
       <c r="S281" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124624537</v>
+        <v>124621864</v>
       </c>
       <c r="B274" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31677,21 +31677,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -31701,10 +31701,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368960</v>
+        <v>368827</v>
       </c>
       <c r="R274" t="n">
-        <v>6938297</v>
+        <v>6937946</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31865,10 +31865,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124622472</v>
+        <v>124624537</v>
       </c>
       <c r="B276" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31881,42 +31881,37 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P276" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368802</v>
+        <v>368960</v>
       </c>
       <c r="R276" t="n">
-        <v>6938048</v>
+        <v>6938297</v>
       </c>
       <c r="S276" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -31972,7 +31967,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124625773</v>
+        <v>124621836</v>
       </c>
       <c r="B277" t="n">
         <v>91030</v>
@@ -32012,10 +32007,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>368933</v>
+        <v>368827</v>
       </c>
       <c r="R277" t="n">
-        <v>6938257</v>
+        <v>6937946</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -32074,10 +32069,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124621864</v>
+        <v>124622472</v>
       </c>
       <c r="B278" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32090,37 +32085,42 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368827</v>
+        <v>368802</v>
       </c>
       <c r="R278" t="n">
-        <v>6937946</v>
+        <v>6938048</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124625410</v>
+        <v>124625773</v>
       </c>
       <c r="B280" t="n">
         <v>91030</v>
@@ -32319,17 +32319,17 @@
       <c r="I280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>369017</v>
+        <v>368933</v>
       </c>
       <c r="R280" t="n">
-        <v>6938332</v>
+        <v>6938257</v>
       </c>
       <c r="S280" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32385,10 +32385,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124621836</v>
+        <v>124624109</v>
       </c>
       <c r="B281" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32401,34 +32401,34 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368827</v>
+        <v>368931</v>
       </c>
       <c r="R281" t="n">
-        <v>6937946</v>
+        <v>6938267</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -32487,10 +32487,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124624109</v>
+        <v>124625410</v>
       </c>
       <c r="B282" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32503,21 +32503,21 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -32527,13 +32527,13 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368931</v>
+        <v>369017</v>
       </c>
       <c r="R282" t="n">
-        <v>6938267</v>
+        <v>6938332</v>
       </c>
       <c r="S282" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124621864</v>
+        <v>124621836</v>
       </c>
       <c r="B274" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31677,21 +31677,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -31763,10 +31763,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124625988</v>
+        <v>124624504</v>
       </c>
       <c r="B275" t="n">
-        <v>91700</v>
+        <v>57513</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31775,41 +31775,46 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>368879</v>
+        <v>368934</v>
       </c>
       <c r="R275" t="n">
-        <v>6938246</v>
+        <v>6938300</v>
       </c>
       <c r="S275" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31865,10 +31870,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124624537</v>
+        <v>124624109</v>
       </c>
       <c r="B276" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31881,34 +31886,34 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368960</v>
+        <v>368931</v>
       </c>
       <c r="R276" t="n">
-        <v>6938297</v>
+        <v>6938267</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31967,7 +31972,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124621836</v>
+        <v>124625410</v>
       </c>
       <c r="B277" t="n">
         <v>91030</v>
@@ -32003,17 +32008,17 @@
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>368827</v>
+        <v>369017</v>
       </c>
       <c r="R277" t="n">
-        <v>6937946</v>
+        <v>6938332</v>
       </c>
       <c r="S277" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -32069,10 +32074,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124622472</v>
+        <v>124624537</v>
       </c>
       <c r="B278" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32085,42 +32090,37 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368802</v>
+        <v>368960</v>
       </c>
       <c r="R278" t="n">
-        <v>6938048</v>
+        <v>6938297</v>
       </c>
       <c r="S278" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -32176,10 +32176,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124624504</v>
+        <v>124625988</v>
       </c>
       <c r="B279" t="n">
-        <v>57513</v>
+        <v>91700</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32188,46 +32188,41 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>368934</v>
+        <v>368879</v>
       </c>
       <c r="R279" t="n">
-        <v>6938300</v>
+        <v>6938246</v>
       </c>
       <c r="S279" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32283,10 +32278,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124625773</v>
+        <v>124621864</v>
       </c>
       <c r="B280" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -32299,21 +32294,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -32323,10 +32318,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>368933</v>
+        <v>368827</v>
       </c>
       <c r="R280" t="n">
-        <v>6938257</v>
+        <v>6937946</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -32385,10 +32380,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124624109</v>
+        <v>124625773</v>
       </c>
       <c r="B281" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32401,34 +32396,34 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368931</v>
+        <v>368933</v>
       </c>
       <c r="R281" t="n">
-        <v>6938267</v>
+        <v>6938257</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -32487,10 +32482,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124625410</v>
+        <v>124622472</v>
       </c>
       <c r="B282" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32503,37 +32498,42 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>369017</v>
+        <v>368802</v>
       </c>
       <c r="R282" t="n">
-        <v>6938332</v>
+        <v>6938048</v>
       </c>
       <c r="S282" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124621836</v>
+        <v>124624109</v>
       </c>
       <c r="B274" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31677,34 +31677,34 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368827</v>
+        <v>368931</v>
       </c>
       <c r="R274" t="n">
-        <v>6937946</v>
+        <v>6938267</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31763,10 +31763,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124624504</v>
+        <v>124625410</v>
       </c>
       <c r="B275" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31779,42 +31779,37 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>368934</v>
+        <v>369017</v>
       </c>
       <c r="R275" t="n">
-        <v>6938300</v>
+        <v>6938332</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31870,10 +31865,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124624109</v>
+        <v>124621864</v>
       </c>
       <c r="B276" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31886,34 +31881,34 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368931</v>
+        <v>368827</v>
       </c>
       <c r="R276" t="n">
-        <v>6938267</v>
+        <v>6937946</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31972,7 +31967,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124625410</v>
+        <v>124624537</v>
       </c>
       <c r="B277" t="n">
         <v>91030</v>
@@ -32008,17 +32003,17 @@
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>369017</v>
+        <v>368960</v>
       </c>
       <c r="R277" t="n">
-        <v>6938332</v>
+        <v>6938297</v>
       </c>
       <c r="S277" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -32074,10 +32069,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124624537</v>
+        <v>124625988</v>
       </c>
       <c r="B278" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32086,41 +32081,41 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368960</v>
+        <v>368879</v>
       </c>
       <c r="R278" t="n">
-        <v>6938297</v>
+        <v>6938246</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -32176,10 +32171,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124625988</v>
+        <v>124625773</v>
       </c>
       <c r="B279" t="n">
-        <v>91700</v>
+        <v>91030</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32188,41 +32183,41 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>368879</v>
+        <v>368933</v>
       </c>
       <c r="R279" t="n">
-        <v>6938246</v>
+        <v>6938257</v>
       </c>
       <c r="S279" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -32278,10 +32273,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124621864</v>
+        <v>124622472</v>
       </c>
       <c r="B280" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -32294,37 +32289,42 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P280" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>368827</v>
+        <v>368802</v>
       </c>
       <c r="R280" t="n">
-        <v>6937946</v>
+        <v>6938048</v>
       </c>
       <c r="S280" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124625773</v>
+        <v>124621836</v>
       </c>
       <c r="B281" t="n">
         <v>91030</v>
@@ -32420,10 +32420,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368933</v>
+        <v>368827</v>
       </c>
       <c r="R281" t="n">
-        <v>6938257</v>
+        <v>6937946</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -32482,7 +32482,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124622472</v>
+        <v>124624504</v>
       </c>
       <c r="B282" t="n">
         <v>57513</v>
@@ -32527,13 +32527,13 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368802</v>
+        <v>368934</v>
       </c>
       <c r="R282" t="n">
-        <v>6938048</v>
+        <v>6938300</v>
       </c>
       <c r="S282" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124624109</v>
+        <v>124625988</v>
       </c>
       <c r="B274" t="n">
-        <v>91008</v>
+        <v>91700</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31673,25 +31673,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -31701,13 +31701,13 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368931</v>
+        <v>368879</v>
       </c>
       <c r="R274" t="n">
-        <v>6938267</v>
+        <v>6938246</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124625410</v>
+        <v>124621836</v>
       </c>
       <c r="B275" t="n">
         <v>91030</v>
@@ -31799,17 +31799,17 @@
       <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>369017</v>
+        <v>368827</v>
       </c>
       <c r="R275" t="n">
-        <v>6938332</v>
+        <v>6937946</v>
       </c>
       <c r="S275" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31865,10 +31865,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124621864</v>
+        <v>124625773</v>
       </c>
       <c r="B276" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31881,21 +31881,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -31905,10 +31905,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368827</v>
+        <v>368933</v>
       </c>
       <c r="R276" t="n">
-        <v>6937946</v>
+        <v>6938257</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31967,10 +31967,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124624537</v>
+        <v>124624504</v>
       </c>
       <c r="B277" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31983,34 +31983,39 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P277" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>368960</v>
+        <v>368934</v>
       </c>
       <c r="R277" t="n">
-        <v>6938297</v>
+        <v>6938300</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -32069,10 +32074,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124625988</v>
+        <v>124622472</v>
       </c>
       <c r="B278" t="n">
-        <v>91700</v>
+        <v>57513</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32081,41 +32086,46 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368879</v>
+        <v>368802</v>
       </c>
       <c r="R278" t="n">
-        <v>6938246</v>
+        <v>6938048</v>
       </c>
       <c r="S278" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -32171,10 +32181,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124625773</v>
+        <v>124624109</v>
       </c>
       <c r="B279" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32187,34 +32197,34 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>368933</v>
+        <v>368931</v>
       </c>
       <c r="R279" t="n">
-        <v>6938257</v>
+        <v>6938267</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -32273,10 +32283,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124622472</v>
+        <v>124624537</v>
       </c>
       <c r="B280" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -32289,42 +32299,37 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P280" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>368802</v>
+        <v>368960</v>
       </c>
       <c r="R280" t="n">
-        <v>6938048</v>
+        <v>6938297</v>
       </c>
       <c r="S280" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32380,10 +32385,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124621836</v>
+        <v>124621864</v>
       </c>
       <c r="B281" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32396,21 +32401,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -32482,10 +32487,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124624504</v>
+        <v>124625410</v>
       </c>
       <c r="B282" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32498,42 +32503,37 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368934</v>
+        <v>369017</v>
       </c>
       <c r="R282" t="n">
-        <v>6938300</v>
+        <v>6938332</v>
       </c>
       <c r="S282" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124625988</v>
+        <v>124624109</v>
       </c>
       <c r="B274" t="n">
-        <v>91700</v>
+        <v>91008</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31673,25 +31673,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -31701,13 +31701,13 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368879</v>
+        <v>368931</v>
       </c>
       <c r="R274" t="n">
-        <v>6938246</v>
+        <v>6938267</v>
       </c>
       <c r="S274" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -31865,10 +31865,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124625773</v>
+        <v>124625988</v>
       </c>
       <c r="B276" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31877,41 +31877,41 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368933</v>
+        <v>368879</v>
       </c>
       <c r="R276" t="n">
-        <v>6938257</v>
+        <v>6938246</v>
       </c>
       <c r="S276" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -31967,10 +31967,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124624504</v>
+        <v>124621864</v>
       </c>
       <c r="B277" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31983,39 +31983,34 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P277" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>368934</v>
+        <v>368827</v>
       </c>
       <c r="R277" t="n">
-        <v>6938300</v>
+        <v>6937946</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -32074,7 +32069,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124622472</v>
+        <v>124624504</v>
       </c>
       <c r="B278" t="n">
         <v>57513</v>
@@ -32119,13 +32114,13 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368802</v>
+        <v>368934</v>
       </c>
       <c r="R278" t="n">
-        <v>6938048</v>
+        <v>6938300</v>
       </c>
       <c r="S278" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -32181,10 +32176,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124624109</v>
+        <v>124624537</v>
       </c>
       <c r="B279" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32197,34 +32192,34 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>368931</v>
+        <v>368960</v>
       </c>
       <c r="R279" t="n">
-        <v>6938267</v>
+        <v>6938297</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -32283,7 +32278,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124624537</v>
+        <v>124625410</v>
       </c>
       <c r="B280" t="n">
         <v>91030</v>
@@ -32319,17 +32314,17 @@
       <c r="I280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>368960</v>
+        <v>369017</v>
       </c>
       <c r="R280" t="n">
-        <v>6938297</v>
+        <v>6938332</v>
       </c>
       <c r="S280" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32385,10 +32380,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124621864</v>
+        <v>124622472</v>
       </c>
       <c r="B281" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32401,37 +32396,42 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P281" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368827</v>
+        <v>368802</v>
       </c>
       <c r="R281" t="n">
-        <v>6937946</v>
+        <v>6938048</v>
       </c>
       <c r="S281" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124625410</v>
+        <v>124625773</v>
       </c>
       <c r="B282" t="n">
         <v>91030</v>
@@ -32523,17 +32523,17 @@
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>369017</v>
+        <v>368933</v>
       </c>
       <c r="R282" t="n">
-        <v>6938332</v>
+        <v>6938257</v>
       </c>
       <c r="S282" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -31661,10 +31661,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124624109</v>
+        <v>124622472</v>
       </c>
       <c r="B274" t="n">
-        <v>91008</v>
+        <v>57635</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31677,37 +31677,42 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>368931</v>
+        <v>368802</v>
       </c>
       <c r="R274" t="n">
-        <v>6938267</v>
+        <v>6938048</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -31763,10 +31768,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124621836</v>
+        <v>124625988</v>
       </c>
       <c r="B275" t="n">
-        <v>91030</v>
+        <v>91860</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31775,41 +31780,41 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>368827</v>
+        <v>368879</v>
       </c>
       <c r="R275" t="n">
-        <v>6937946</v>
+        <v>6938246</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31865,10 +31870,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124625988</v>
+        <v>124625773</v>
       </c>
       <c r="B276" t="n">
-        <v>91700</v>
+        <v>91184</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31877,41 +31882,41 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368879</v>
+        <v>368933</v>
       </c>
       <c r="R276" t="n">
-        <v>6938246</v>
+        <v>6938257</v>
       </c>
       <c r="S276" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -31967,10 +31972,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124621864</v>
+        <v>124624109</v>
       </c>
       <c r="B277" t="n">
-        <v>78810</v>
+        <v>91162</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31983,34 +31988,34 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>368827</v>
+        <v>368931</v>
       </c>
       <c r="R277" t="n">
-        <v>6937946</v>
+        <v>6938267</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -32069,10 +32074,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124624504</v>
+        <v>124621836</v>
       </c>
       <c r="B278" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -32085,39 +32090,34 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>368934</v>
+        <v>368827</v>
       </c>
       <c r="R278" t="n">
-        <v>6938300</v>
+        <v>6937946</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32179,7 +32179,7 @@
         <v>124624537</v>
       </c>
       <c r="B279" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -32278,10 +32278,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124625410</v>
+        <v>124624504</v>
       </c>
       <c r="B280" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -32294,37 +32294,42 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>369017</v>
+        <v>368934</v>
       </c>
       <c r="R280" t="n">
-        <v>6938332</v>
+        <v>6938300</v>
       </c>
       <c r="S280" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -32380,10 +32385,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124622472</v>
+        <v>124625410</v>
       </c>
       <c r="B281" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -32396,42 +32401,37 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>368802</v>
+        <v>369017</v>
       </c>
       <c r="R281" t="n">
-        <v>6938048</v>
+        <v>6938332</v>
       </c>
       <c r="S281" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -32487,10 +32487,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124625773</v>
+        <v>124621864</v>
       </c>
       <c r="B282" t="n">
-        <v>91030</v>
+        <v>78947</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -32503,21 +32503,21 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -32527,10 +32527,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>368933</v>
+        <v>368827</v>
       </c>
       <c r="R282" t="n">
-        <v>6938257</v>
+        <v>6937946</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY282"/>
+  <dimension ref="A1:AY283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32587,6 +32587,131 @@
       </c>
       <c r="AY282" t="inlineStr"/>
     </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>125696719</v>
+      </c>
+      <c r="B283" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr"/>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Backvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>368750</v>
+      </c>
+      <c r="R283" t="n">
+        <v>6937906</v>
+      </c>
+      <c r="S283" t="n">
+        <v>10</v>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>Ringhack i granar, fanns äldre i närheten också</t>
+        </is>
+      </c>
+      <c r="AD283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT283" t="inlineStr"/>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Martin Blomberg</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>Martin Blomberg</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -32592,12 +32592,7 @@
         <v>125696719</v>
       </c>
       <c r="B283" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -32592,7 +32592,7 @@
         <v>125696719</v>
       </c>
       <c r="B283" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -32592,7 +32592,7 @@
         <v>125696719</v>
       </c>
       <c r="B283" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>96971</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368990.6208162205</v>
+        <v>368991</v>
       </c>
       <c r="R2" t="n">
-        <v>6938510.760126672</v>
+        <v>6938511</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1965-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1994-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>99251</v>
+        <v>99257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>99257</v>
+        <v>99260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>99260</v>
+        <v>99265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>99299</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>99310</v>
+        <v>99317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>99320</v>
+        <v>99325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56732438</v>
       </c>
       <c r="B2" t="n">
-        <v>99325</v>
+        <v>99333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -12646,7 +12646,7 @@
         <v>0</v>
       </c>
       <c r="AE107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG107" t="b">
         <v>0</v>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY283"/>
+  <dimension ref="A1:AY287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32692,6 +32692,466 @@
       </c>
       <c r="AY283" t="inlineStr"/>
     </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>131327393</v>
+      </c>
+      <c r="B284" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>Ytteränget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>369418</v>
+      </c>
+      <c r="R284" t="n">
+        <v>6938342</v>
+      </c>
+      <c r="S284" t="n">
+        <v>6</v>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT284" t="inlineStr"/>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Tobias Ljungquist</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>Tobias Ljungquist</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>131327395</v>
+      </c>
+      <c r="B285" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>Ytteränget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>369418</v>
+      </c>
+      <c r="R285" t="n">
+        <v>6938342</v>
+      </c>
+      <c r="S285" t="n">
+        <v>6</v>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT285" t="inlineStr"/>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>Tobias Ljungquist</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>Tobias Ljungquist</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>131327396</v>
+      </c>
+      <c r="B286" t="n">
+        <v>58521</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Ytteränget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>369418</v>
+      </c>
+      <c r="R286" t="n">
+        <v>6938342</v>
+      </c>
+      <c r="S286" t="n">
+        <v>6</v>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT286" t="inlineStr"/>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>Tobias Ljungquist</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>Tobias Ljungquist</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>131327394</v>
+      </c>
+      <c r="B287" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>Ytteränget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q287" t="n">
+        <v>369418</v>
+      </c>
+      <c r="R287" t="n">
+        <v>6938342</v>
+      </c>
+      <c r="S287" t="n">
+        <v>6</v>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT287" t="inlineStr"/>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Tobias Ljungquist</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>Tobias Ljungquist</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -32697,7 +32697,7 @@
         <v>131327393</v>
       </c>
       <c r="B284" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>131327395</v>
       </c>
       <c r="B285" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>131327396</v>
       </c>
       <c r="B286" t="n">
-        <v>58521</v>
+        <v>58523</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>131327394</v>
       </c>
       <c r="B287" t="n">
-        <v>57988</v>
+        <v>57990</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -32697,7 +32697,7 @@
         <v>131327393</v>
       </c>
       <c r="B284" t="n">
-        <v>57727</v>
+        <v>57728</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>131327395</v>
       </c>
       <c r="B285" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>131327396</v>
       </c>
       <c r="B286" t="n">
-        <v>58523</v>
+        <v>58524</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>131327394</v>
       </c>
       <c r="B287" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -32697,7 +32697,7 @@
         <v>131327393</v>
       </c>
       <c r="B284" t="n">
-        <v>57733</v>
+        <v>57739</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>131327395</v>
       </c>
       <c r="B285" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>131327396</v>
       </c>
       <c r="B286" t="n">
-        <v>58529</v>
+        <v>58535</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>131327394</v>
       </c>
       <c r="B287" t="n">
-        <v>57996</v>
+        <v>58002</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -32697,7 +32697,7 @@
         <v>131327393</v>
       </c>
       <c r="B284" t="n">
-        <v>57739</v>
+        <v>57740</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>131327395</v>
       </c>
       <c r="B285" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>131327396</v>
       </c>
       <c r="B286" t="n">
-        <v>58535</v>
+        <v>58536</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>131327394</v>
       </c>
       <c r="B287" t="n">
-        <v>58002</v>
+        <v>58003</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -32697,7 +32697,7 @@
         <v>131327393</v>
       </c>
       <c r="B284" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>131327395</v>
       </c>
       <c r="B285" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>131327396</v>
       </c>
       <c r="B286" t="n">
-        <v>58536</v>
+        <v>58539</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>131327394</v>
       </c>
       <c r="B287" t="n">
-        <v>58003</v>
+        <v>58006</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -32697,7 +32697,7 @@
         <v>131327393</v>
       </c>
       <c r="B284" t="n">
-        <v>57743</v>
+        <v>57745</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>131327395</v>
       </c>
       <c r="B285" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>131327396</v>
       </c>
       <c r="B286" t="n">
-        <v>58539</v>
+        <v>58541</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>131327394</v>
       </c>
       <c r="B287" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY300"/>
+  <dimension ref="A1:AY301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11697,10 +11697,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>103582817</v>
+        <v>134473952</v>
       </c>
       <c r="B112" t="n">
-        <v>58057</v>
+        <v>57975</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11708,16 +11708,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11726,20 +11726,24 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>369385</v>
+        <v>368788</v>
       </c>
       <c r="R112" t="n">
-        <v>6938131</v>
+        <v>6937894</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11763,12 +11767,27 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Färska ringhack i flertalet granar</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11783,19 +11802,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Camilla Pakka</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Camilla Pakka</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>108379968</v>
+        <v>103582817</v>
       </c>
       <c r="B113" t="n">
         <v>58057</v>
@@ -11823,29 +11842,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>368776</v>
+        <v>369385</v>
       </c>
       <c r="R113" t="n">
-        <v>6938113</v>
+        <v>6938131</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -11872,12 +11880,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11904,10 +11912,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>103556881</v>
+        <v>108379968</v>
       </c>
       <c r="B114" t="n">
-        <v>81332</v>
+        <v>58057</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11915,35 +11923,46 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229436</v>
+        <v>103031</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>368809</v>
+        <v>368776</v>
       </c>
       <c r="R114" t="n">
-        <v>6938211</v>
+        <v>6938113</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -11970,12 +11989,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12002,46 +12021,46 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>107045266</v>
+        <v>103556881</v>
       </c>
       <c r="B115" t="n">
-        <v>92637</v>
+        <v>81332</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>67</v>
+        <v>229436</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Ytteränget, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>369416</v>
+        <v>368809</v>
       </c>
       <c r="R115" t="n">
-        <v>6938307</v>
+        <v>6938211</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12068,12 +12087,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12100,7 +12119,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>107046233</v>
+        <v>107045266</v>
       </c>
       <c r="B116" t="n">
         <v>92637</v>
@@ -12136,10 +12155,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>369294</v>
+        <v>369416</v>
       </c>
       <c r="R116" t="n">
-        <v>6938382</v>
+        <v>6938307</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12198,10 +12217,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>56732438</v>
+        <v>107046233</v>
       </c>
       <c r="B117" t="n">
-        <v>99800</v>
+        <v>92637</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12209,37 +12228,38 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>260</v>
+        <v>67</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Myrstarr</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carex heleonastes</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Ehrh. ex L.f.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Linvallen, 1 km NV om, Hjd</t>
+          <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>368991</v>
+        <v>369294</v>
       </c>
       <c r="R117" t="n">
-        <v>6938511</v>
+        <v>6938382</v>
       </c>
       <c r="S117" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12263,17 +12283,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>1965-01-01</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>1994-12-31</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>G Holmström</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12284,74 +12299,64 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>Myrmark</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bengt Danielsson</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr">
-        <is>
-          <t>Härjedalens kärlväxtflora 1994</t>
-        </is>
-      </c>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>103557130</v>
+        <v>56732438</v>
       </c>
       <c r="B118" t="n">
-        <v>83292</v>
+        <v>99800</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Myrstarr</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Carex heleonastes</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Ehrh. ex L.f.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Linvallen, 1 km NV om, Hjd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>368828</v>
+        <v>368991</v>
       </c>
       <c r="R118" t="n">
-        <v>6938287</v>
+        <v>6938511</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12375,12 +12380,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>1965-01-01</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>1994-12-31</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>G Holmström</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12391,62 +12401,71 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Myrmark</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
+          <t>Bengt Danielsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>Härjedalens kärlväxtflora 1994</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>107045154</v>
+        <v>103557130</v>
       </c>
       <c r="B119" t="n">
-        <v>78350</v>
+        <v>83292</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Ytteränget, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>369441</v>
+        <v>368828</v>
       </c>
       <c r="R119" t="n">
-        <v>6938289</v>
+        <v>6938287</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12473,12 +12492,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12505,10 +12524,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>103557237</v>
+        <v>107045154</v>
       </c>
       <c r="B120" t="n">
-        <v>78686</v>
+        <v>78350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12516,35 +12535,35 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>498</v>
+        <v>314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>368851</v>
+        <v>369441</v>
       </c>
       <c r="R120" t="n">
-        <v>6938304</v>
+        <v>6938289</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12571,12 +12590,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12603,7 +12622,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>103582073</v>
+        <v>103557237</v>
       </c>
       <c r="B121" t="n">
         <v>78686</v>
@@ -12639,10 +12658,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>369661</v>
+        <v>368851</v>
       </c>
       <c r="R121" t="n">
-        <v>6938280</v>
+        <v>6938304</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -12669,12 +12688,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12701,7 +12720,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>103583919</v>
+        <v>103582073</v>
       </c>
       <c r="B122" t="n">
         <v>78686</v>
@@ -12737,10 +12756,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>369061</v>
+        <v>369661</v>
       </c>
       <c r="R122" t="n">
-        <v>6938242</v>
+        <v>6938280</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -12799,32 +12818,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>103585484</v>
+        <v>103583919</v>
       </c>
       <c r="B123" t="n">
-        <v>79406</v>
+        <v>78686</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>864</v>
+        <v>498</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12835,10 +12854,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>368900</v>
+        <v>369061</v>
       </c>
       <c r="R123" t="n">
-        <v>6938283</v>
+        <v>6938242</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -12897,7 +12916,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>107045050</v>
+        <v>103585484</v>
       </c>
       <c r="B124" t="n">
         <v>79406</v>
@@ -12929,14 +12948,14 @@
       <c r="K124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ytteränget, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>369452</v>
+        <v>368900</v>
       </c>
       <c r="R124" t="n">
-        <v>6938304</v>
+        <v>6938283</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -12963,12 +12982,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12995,46 +13014,46 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>103582287</v>
+        <v>107045050</v>
       </c>
       <c r="B125" t="n">
-        <v>92662</v>
+        <v>79406</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1105</v>
+        <v>864</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>369610</v>
+        <v>369452</v>
       </c>
       <c r="R125" t="n">
-        <v>6938297</v>
+        <v>6938304</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13061,19 +13080,19 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="b">
         <v>0</v>
@@ -13093,32 +13112,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>103565379</v>
+        <v>103582287</v>
       </c>
       <c r="B126" t="n">
-        <v>91905</v>
+        <v>92662</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13129,10 +13148,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>369265</v>
+        <v>369610</v>
       </c>
       <c r="R126" t="n">
-        <v>6938424</v>
+        <v>6938297</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13159,19 +13178,19 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG126" t="b">
         <v>0</v>
@@ -13191,7 +13210,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>103568498</v>
+        <v>103565379</v>
       </c>
       <c r="B127" t="n">
         <v>91905</v>
@@ -13223,14 +13242,14 @@
       <c r="K127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>369022</v>
+        <v>369265</v>
       </c>
       <c r="R127" t="n">
-        <v>6938564</v>
+        <v>6938424</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13289,7 +13308,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>103582206</v>
+        <v>103568498</v>
       </c>
       <c r="B128" t="n">
         <v>91905</v>
@@ -13325,10 +13344,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>369666</v>
+        <v>369022</v>
       </c>
       <c r="R128" t="n">
-        <v>6938285</v>
+        <v>6938564</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13355,12 +13374,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13387,7 +13406,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>107046935</v>
+        <v>103582206</v>
       </c>
       <c r="B129" t="n">
         <v>91905</v>
@@ -13419,14 +13438,14 @@
       <c r="K129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Ytteränget, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>369008</v>
+        <v>369666</v>
       </c>
       <c r="R129" t="n">
-        <v>6938441</v>
+        <v>6938285</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13453,12 +13472,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13485,7 +13504,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124624109</v>
+        <v>107046935</v>
       </c>
       <c r="B130" t="n">
         <v>91905</v>
@@ -13514,19 +13533,20 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>368931</v>
+        <v>369008</v>
       </c>
       <c r="R130" t="n">
-        <v>6938267</v>
+        <v>6938441</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13550,12 +13570,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13582,10 +13602,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>103584120</v>
+        <v>124624109</v>
       </c>
       <c r="B131" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13593,38 +13613,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>369130</v>
+        <v>368931</v>
       </c>
       <c r="R131" t="n">
-        <v>6938320</v>
+        <v>6938267</v>
       </c>
       <c r="S131" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13648,12 +13667,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13680,32 +13699,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>103568492</v>
+        <v>103584120</v>
       </c>
       <c r="B132" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13716,10 +13735,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>369022</v>
+        <v>369130</v>
       </c>
       <c r="R132" t="n">
-        <v>6938564</v>
+        <v>6938320</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -13746,12 +13765,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13778,32 +13797,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>103568328</v>
+        <v>103568492</v>
       </c>
       <c r="B133" t="n">
-        <v>92369</v>
+        <v>91923</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13814,10 +13833,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>368899</v>
+        <v>369022</v>
       </c>
       <c r="R133" t="n">
-        <v>6938467</v>
+        <v>6938564</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -13876,10 +13895,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>96505248</v>
+        <v>103568328</v>
       </c>
       <c r="B134" t="n">
-        <v>83173</v>
+        <v>92369</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13887,35 +13906,35 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>369523</v>
+        <v>368899</v>
       </c>
       <c r="R134" t="n">
-        <v>6938214</v>
+        <v>6938467</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -13942,12 +13961,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13974,7 +13993,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>96506895</v>
+        <v>96505248</v>
       </c>
       <c r="B135" t="n">
         <v>83173</v>
@@ -14010,10 +14029,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>369571</v>
+        <v>369523</v>
       </c>
       <c r="R135" t="n">
-        <v>6938216</v>
+        <v>6938214</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14072,7 +14091,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>103565802</v>
+        <v>96506895</v>
       </c>
       <c r="B136" t="n">
         <v>83173</v>
@@ -14104,14 +14123,14 @@
       <c r="K136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>369101</v>
+        <v>369571</v>
       </c>
       <c r="R136" t="n">
-        <v>6938442</v>
+        <v>6938216</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14138,12 +14157,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14170,7 +14189,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>103566573</v>
+        <v>103565802</v>
       </c>
       <c r="B137" t="n">
         <v>83173</v>
@@ -14206,10 +14225,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>368840</v>
+        <v>369101</v>
       </c>
       <c r="R137" t="n">
-        <v>6938243</v>
+        <v>6938442</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14268,7 +14287,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>103568390</v>
+        <v>103566573</v>
       </c>
       <c r="B138" t="n">
         <v>83173</v>
@@ -14304,10 +14323,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>368943</v>
+        <v>368840</v>
       </c>
       <c r="R138" t="n">
-        <v>6938568</v>
+        <v>6938243</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -14366,7 +14385,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>103582020</v>
+        <v>103568390</v>
       </c>
       <c r="B139" t="n">
         <v>83173</v>
@@ -14402,10 +14421,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>369675</v>
+        <v>368943</v>
       </c>
       <c r="R139" t="n">
-        <v>6938240</v>
+        <v>6938568</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14432,12 +14451,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14464,7 +14483,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>103582551</v>
+        <v>103582020</v>
       </c>
       <c r="B140" t="n">
         <v>83173</v>
@@ -14496,14 +14515,14 @@
       <c r="K140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>369596</v>
+        <v>369675</v>
       </c>
       <c r="R140" t="n">
-        <v>6938292</v>
+        <v>6938240</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14562,7 +14581,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>103584062</v>
+        <v>103582551</v>
       </c>
       <c r="B141" t="n">
         <v>83173</v>
@@ -14594,14 +14613,14 @@
       <c r="K141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>369120</v>
+        <v>369596</v>
       </c>
       <c r="R141" t="n">
-        <v>6938224</v>
+        <v>6938292</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -14660,7 +14679,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>103584153</v>
+        <v>103584062</v>
       </c>
       <c r="B142" t="n">
         <v>83173</v>
@@ -14696,10 +14715,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>369113</v>
+        <v>369120</v>
       </c>
       <c r="R142" t="n">
-        <v>6938334</v>
+        <v>6938224</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -14758,7 +14777,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>103585541</v>
+        <v>103584153</v>
       </c>
       <c r="B143" t="n">
         <v>83173</v>
@@ -14794,10 +14813,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>368911</v>
+        <v>369113</v>
       </c>
       <c r="R143" t="n">
-        <v>6938305</v>
+        <v>6938334</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -14856,7 +14875,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>107033511</v>
+        <v>103585541</v>
       </c>
       <c r="B144" t="n">
         <v>83173</v>
@@ -14888,14 +14907,14 @@
       <c r="K144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>369012</v>
+        <v>368911</v>
       </c>
       <c r="R144" t="n">
-        <v>6938275</v>
+        <v>6938305</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -14922,12 +14941,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -14954,7 +14973,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>107045102</v>
+        <v>107033511</v>
       </c>
       <c r="B145" t="n">
         <v>83173</v>
@@ -14986,14 +15005,14 @@
       <c r="K145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Ytteränget, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>369440</v>
+        <v>369012</v>
       </c>
       <c r="R145" t="n">
-        <v>6938294</v>
+        <v>6938275</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15020,12 +15039,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15052,7 +15071,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>107045305</v>
+        <v>107045102</v>
       </c>
       <c r="B146" t="n">
         <v>83173</v>
@@ -15088,10 +15107,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>369397</v>
+        <v>369440</v>
       </c>
       <c r="R146" t="n">
-        <v>6938322</v>
+        <v>6938294</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15150,7 +15169,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>108002141</v>
+        <v>107045305</v>
       </c>
       <c r="B147" t="n">
         <v>83173</v>
@@ -15178,11 +15197,7 @@
           <t>(Nyl.) Rehm</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
@@ -15190,10 +15205,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>369148</v>
+        <v>369397</v>
       </c>
       <c r="R147" t="n">
-        <v>6938404</v>
+        <v>6938322</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -15220,22 +15235,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15250,19 +15255,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>108002997</v>
+        <v>108002141</v>
       </c>
       <c r="B148" t="n">
         <v>83173</v>
@@ -15302,10 +15307,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>369149</v>
+        <v>369148</v>
       </c>
       <c r="R148" t="n">
-        <v>6938437</v>
+        <v>6938404</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -15337,7 +15342,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15347,7 +15352,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15374,7 +15379,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>108003507</v>
+        <v>108002997</v>
       </c>
       <c r="B149" t="n">
         <v>83173</v>
@@ -15402,7 +15407,11 @@
           <t>(Nyl.) Rehm</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -15410,10 +15419,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>369137</v>
+        <v>369149</v>
       </c>
       <c r="R149" t="n">
-        <v>6938429</v>
+        <v>6938437</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15443,9 +15452,19 @@
           <t>2023-04-10</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15460,19 +15479,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>108003827</v>
+        <v>108003507</v>
       </c>
       <c r="B150" t="n">
         <v>83173</v>
@@ -15508,10 +15527,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>369101</v>
+        <v>369137</v>
       </c>
       <c r="R150" t="n">
-        <v>6938449</v>
+        <v>6938429</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -15570,7 +15589,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>108005011</v>
+        <v>108003827</v>
       </c>
       <c r="B151" t="n">
         <v>83173</v>
@@ -15606,10 +15625,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368980</v>
+        <v>369101</v>
       </c>
       <c r="R151" t="n">
-        <v>6938466</v>
+        <v>6938449</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -15639,19 +15658,9 @@
           <t>2023-04-10</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>16:49</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15666,19 +15675,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>108006998</v>
+        <v>108005011</v>
       </c>
       <c r="B152" t="n">
         <v>83173</v>
@@ -15706,22 +15715,18 @@
           <t>(Nyl.) Rehm</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368882</v>
+        <v>368980</v>
       </c>
       <c r="R152" t="n">
-        <v>6938333</v>
+        <v>6938466</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -15753,7 +15758,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -15763,7 +15768,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15790,10 +15795,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>103568460</v>
+        <v>108006998</v>
       </c>
       <c r="B153" t="n">
-        <v>83312</v>
+        <v>83173</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15801,35 +15806,39 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368969</v>
+        <v>368882</v>
       </c>
       <c r="R153" t="n">
-        <v>6938580</v>
+        <v>6938333</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -15856,12 +15865,22 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -15876,44 +15895,44 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>103568309</v>
+        <v>103568460</v>
       </c>
       <c r="B154" t="n">
-        <v>92283</v>
+        <v>83312</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2063</v>
+        <v>1467</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15924,10 +15943,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368876</v>
+        <v>368969</v>
       </c>
       <c r="R154" t="n">
-        <v>6938448</v>
+        <v>6938580</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -15986,45 +16005,46 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124625988</v>
+        <v>103568309</v>
       </c>
       <c r="B155" t="n">
-        <v>92632</v>
+        <v>92283</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3298</v>
+        <v>2063</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368879</v>
+        <v>368876</v>
       </c>
       <c r="R155" t="n">
-        <v>6938246</v>
+        <v>6938448</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -16051,12 +16071,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16083,46 +16103,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>96505244</v>
+        <v>124625988</v>
       </c>
       <c r="B156" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>369523</v>
+        <v>368879</v>
       </c>
       <c r="R156" t="n">
-        <v>6938214</v>
+        <v>6938246</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16149,12 +16168,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16181,7 +16200,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>96507218</v>
+        <v>96505244</v>
       </c>
       <c r="B157" t="n">
         <v>79327</v>
@@ -16217,10 +16236,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>369488</v>
+        <v>369523</v>
       </c>
       <c r="R157" t="n">
-        <v>6938216</v>
+        <v>6938214</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -16279,7 +16298,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>97690511</v>
+        <v>96507218</v>
       </c>
       <c r="B158" t="n">
         <v>79327</v>
@@ -16311,14 +16330,14 @@
       <c r="K158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>369088</v>
+        <v>369488</v>
       </c>
       <c r="R158" t="n">
-        <v>6938367</v>
+        <v>6938216</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -16345,12 +16364,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16377,7 +16396,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>97691012</v>
+        <v>97690511</v>
       </c>
       <c r="B159" t="n">
         <v>79327</v>
@@ -16413,10 +16432,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>369171</v>
+        <v>369088</v>
       </c>
       <c r="R159" t="n">
-        <v>6938294</v>
+        <v>6938367</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16475,7 +16494,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>97691090</v>
+        <v>97691012</v>
       </c>
       <c r="B160" t="n">
         <v>79327</v>
@@ -16511,10 +16530,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>369206</v>
+        <v>369171</v>
       </c>
       <c r="R160" t="n">
-        <v>6938324</v>
+        <v>6938294</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -16573,7 +16592,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>103557178</v>
+        <v>97691090</v>
       </c>
       <c r="B161" t="n">
         <v>79327</v>
@@ -16609,10 +16628,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>368850</v>
+        <v>369206</v>
       </c>
       <c r="R161" t="n">
-        <v>6938303</v>
+        <v>6938324</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -16639,12 +16658,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16671,7 +16690,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>103568335</v>
+        <v>103557178</v>
       </c>
       <c r="B162" t="n">
         <v>79327</v>
@@ -16707,10 +16726,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>368915</v>
+        <v>368850</v>
       </c>
       <c r="R162" t="n">
-        <v>6938503</v>
+        <v>6938303</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -16737,12 +16756,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16769,7 +16788,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>103568624</v>
+        <v>103568335</v>
       </c>
       <c r="B163" t="n">
         <v>79327</v>
@@ -16801,14 +16820,14 @@
       <c r="K163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>369030</v>
+        <v>368915</v>
       </c>
       <c r="R163" t="n">
-        <v>6938692</v>
+        <v>6938503</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -16867,7 +16886,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>103568740</v>
+        <v>103568624</v>
       </c>
       <c r="B164" t="n">
         <v>79327</v>
@@ -16903,10 +16922,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>369161</v>
+        <v>369030</v>
       </c>
       <c r="R164" t="n">
-        <v>6938633</v>
+        <v>6938692</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -16965,7 +16984,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>103568794</v>
+        <v>103568740</v>
       </c>
       <c r="B165" t="n">
         <v>79327</v>
@@ -17001,10 +17020,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>369243</v>
+        <v>369161</v>
       </c>
       <c r="R165" t="n">
-        <v>6938488</v>
+        <v>6938633</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -17063,7 +17082,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>103581862</v>
+        <v>103568794</v>
       </c>
       <c r="B166" t="n">
         <v>79327</v>
@@ -17099,10 +17118,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>369549</v>
+        <v>369243</v>
       </c>
       <c r="R166" t="n">
-        <v>6938234</v>
+        <v>6938488</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -17129,12 +17148,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17161,7 +17180,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>103582233</v>
+        <v>103581862</v>
       </c>
       <c r="B167" t="n">
         <v>79327</v>
@@ -17193,14 +17212,14 @@
       <c r="K167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>369619</v>
+        <v>369549</v>
       </c>
       <c r="R167" t="n">
-        <v>6938292</v>
+        <v>6938234</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17259,7 +17278,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>103582617</v>
+        <v>103582233</v>
       </c>
       <c r="B168" t="n">
         <v>79327</v>
@@ -17291,14 +17310,14 @@
       <c r="K168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>369539</v>
+        <v>369619</v>
       </c>
       <c r="R168" t="n">
-        <v>6938259</v>
+        <v>6938292</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -17357,7 +17376,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>103583833</v>
+        <v>103582617</v>
       </c>
       <c r="B169" t="n">
         <v>79327</v>
@@ -17389,14 +17408,14 @@
       <c r="K169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>368970</v>
+        <v>369539</v>
       </c>
       <c r="R169" t="n">
-        <v>6938265</v>
+        <v>6938259</v>
       </c>
       <c r="S169" t="n">
         <v>25</v>
@@ -17455,7 +17474,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>103583847</v>
+        <v>103583833</v>
       </c>
       <c r="B170" t="n">
         <v>79327</v>
@@ -17491,10 +17510,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>369007</v>
+        <v>368970</v>
       </c>
       <c r="R170" t="n">
-        <v>6938296</v>
+        <v>6938265</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -17553,7 +17572,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>103583875</v>
+        <v>103583847</v>
       </c>
       <c r="B171" t="n">
         <v>79327</v>
@@ -17589,10 +17608,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>369040</v>
+        <v>369007</v>
       </c>
       <c r="R171" t="n">
-        <v>6938252</v>
+        <v>6938296</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>
@@ -17651,7 +17670,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>103583929</v>
+        <v>103583875</v>
       </c>
       <c r="B172" t="n">
         <v>79327</v>
@@ -17687,10 +17706,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>369061</v>
+        <v>369040</v>
       </c>
       <c r="R172" t="n">
-        <v>6938242</v>
+        <v>6938252</v>
       </c>
       <c r="S172" t="n">
         <v>25</v>
@@ -17749,7 +17768,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>103584004</v>
+        <v>103583929</v>
       </c>
       <c r="B173" t="n">
         <v>79327</v>
@@ -17785,10 +17804,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>369091</v>
+        <v>369061</v>
       </c>
       <c r="R173" t="n">
-        <v>6938228</v>
+        <v>6938242</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -17847,7 +17866,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>103584077</v>
+        <v>103584004</v>
       </c>
       <c r="B174" t="n">
         <v>79327</v>
@@ -17883,10 +17902,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>369120</v>
+        <v>369091</v>
       </c>
       <c r="R174" t="n">
-        <v>6938263</v>
+        <v>6938228</v>
       </c>
       <c r="S174" t="n">
         <v>25</v>
@@ -17945,7 +17964,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>103584124</v>
+        <v>103584077</v>
       </c>
       <c r="B175" t="n">
         <v>79327</v>
@@ -17981,10 +18000,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>369130</v>
+        <v>369120</v>
       </c>
       <c r="R175" t="n">
-        <v>6938320</v>
+        <v>6938263</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -18043,7 +18062,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>103584200</v>
+        <v>103584124</v>
       </c>
       <c r="B176" t="n">
         <v>79327</v>
@@ -18079,10 +18098,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>369046</v>
+        <v>369130</v>
       </c>
       <c r="R176" t="n">
-        <v>6938345</v>
+        <v>6938320</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -18141,7 +18160,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>103584236</v>
+        <v>103584200</v>
       </c>
       <c r="B177" t="n">
         <v>79327</v>
@@ -18177,10 +18196,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>368985</v>
+        <v>369046</v>
       </c>
       <c r="R177" t="n">
-        <v>6938299</v>
+        <v>6938345</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -18239,7 +18258,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>103585490</v>
+        <v>103584236</v>
       </c>
       <c r="B178" t="n">
         <v>79327</v>
@@ -18275,10 +18294,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>368900</v>
+        <v>368985</v>
       </c>
       <c r="R178" t="n">
-        <v>6938283</v>
+        <v>6938299</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -18337,7 +18356,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>103585509</v>
+        <v>103585490</v>
       </c>
       <c r="B179" t="n">
         <v>79327</v>
@@ -18373,10 +18392,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>368880</v>
+        <v>368900</v>
       </c>
       <c r="R179" t="n">
-        <v>6938305</v>
+        <v>6938283</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -18435,7 +18454,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>103585633</v>
+        <v>103585509</v>
       </c>
       <c r="B180" t="n">
         <v>79327</v>
@@ -18471,10 +18490,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>368882</v>
+        <v>368880</v>
       </c>
       <c r="R180" t="n">
-        <v>6938353</v>
+        <v>6938305</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -18533,7 +18552,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>107032765</v>
+        <v>103585633</v>
       </c>
       <c r="B181" t="n">
         <v>79327</v>
@@ -18565,14 +18584,14 @@
       <c r="K181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>368898</v>
+        <v>368882</v>
       </c>
       <c r="R181" t="n">
-        <v>6938222</v>
+        <v>6938353</v>
       </c>
       <c r="S181" t="n">
         <v>25</v>
@@ -18599,12 +18618,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18631,7 +18650,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>107032923</v>
+        <v>107032765</v>
       </c>
       <c r="B182" t="n">
         <v>79327</v>
@@ -18667,10 +18686,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368903</v>
+        <v>368898</v>
       </c>
       <c r="R182" t="n">
-        <v>6938218</v>
+        <v>6938222</v>
       </c>
       <c r="S182" t="n">
         <v>25</v>
@@ -18729,7 +18748,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>107033002</v>
+        <v>107032923</v>
       </c>
       <c r="B183" t="n">
         <v>79327</v>
@@ -18765,10 +18784,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368929</v>
+        <v>368903</v>
       </c>
       <c r="R183" t="n">
-        <v>6938216</v>
+        <v>6938218</v>
       </c>
       <c r="S183" t="n">
         <v>25</v>
@@ -18827,7 +18846,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>107033401</v>
+        <v>107033002</v>
       </c>
       <c r="B184" t="n">
         <v>79327</v>
@@ -18863,10 +18882,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>369037</v>
+        <v>368929</v>
       </c>
       <c r="R184" t="n">
-        <v>6938226</v>
+        <v>6938216</v>
       </c>
       <c r="S184" t="n">
         <v>25</v>
@@ -18925,7 +18944,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>107033415</v>
+        <v>107033401</v>
       </c>
       <c r="B185" t="n">
         <v>79327</v>
@@ -18961,7 +18980,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>369061</v>
+        <v>369037</v>
       </c>
       <c r="R185" t="n">
         <v>6938226</v>
@@ -19023,7 +19042,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>107033467</v>
+        <v>107033415</v>
       </c>
       <c r="B186" t="n">
         <v>79327</v>
@@ -19059,10 +19078,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>369058</v>
+        <v>369061</v>
       </c>
       <c r="R186" t="n">
-        <v>6938255</v>
+        <v>6938226</v>
       </c>
       <c r="S186" t="n">
         <v>25</v>
@@ -19121,7 +19140,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>107033524</v>
+        <v>107033467</v>
       </c>
       <c r="B187" t="n">
         <v>79327</v>
@@ -19157,10 +19176,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>369007</v>
+        <v>369058</v>
       </c>
       <c r="R187" t="n">
-        <v>6938273</v>
+        <v>6938255</v>
       </c>
       <c r="S187" t="n">
         <v>25</v>
@@ -19219,7 +19238,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>107045001</v>
+        <v>107033524</v>
       </c>
       <c r="B188" t="n">
         <v>79327</v>
@@ -19251,14 +19270,14 @@
       <c r="K188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Ytteränget, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>369464</v>
+        <v>369007</v>
       </c>
       <c r="R188" t="n">
-        <v>6938301</v>
+        <v>6938273</v>
       </c>
       <c r="S188" t="n">
         <v>25</v>
@@ -19285,12 +19304,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -19317,7 +19336,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>107045347</v>
+        <v>107045001</v>
       </c>
       <c r="B189" t="n">
         <v>79327</v>
@@ -19353,10 +19372,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>369415</v>
+        <v>369464</v>
       </c>
       <c r="R189" t="n">
-        <v>6938319</v>
+        <v>6938301</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>
@@ -19415,7 +19434,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>107045393</v>
+        <v>107045347</v>
       </c>
       <c r="B190" t="n">
         <v>79327</v>
@@ -19451,10 +19470,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>369416</v>
+        <v>369415</v>
       </c>
       <c r="R190" t="n">
-        <v>6938346</v>
+        <v>6938319</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -19513,7 +19532,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>107045458</v>
+        <v>107045393</v>
       </c>
       <c r="B191" t="n">
         <v>79327</v>
@@ -19549,10 +19568,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>369397</v>
+        <v>369416</v>
       </c>
       <c r="R191" t="n">
-        <v>6938347</v>
+        <v>6938346</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -19611,7 +19630,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>107045643</v>
+        <v>107045458</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -19647,10 +19666,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>369352</v>
+        <v>369397</v>
       </c>
       <c r="R192" t="n">
-        <v>6938336</v>
+        <v>6938347</v>
       </c>
       <c r="S192" t="n">
         <v>25</v>
@@ -19709,7 +19728,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>107045799</v>
+        <v>107045643</v>
       </c>
       <c r="B193" t="n">
         <v>79327</v>
@@ -19745,10 +19764,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>369339</v>
+        <v>369352</v>
       </c>
       <c r="R193" t="n">
-        <v>6938367</v>
+        <v>6938336</v>
       </c>
       <c r="S193" t="n">
         <v>25</v>
@@ -19807,7 +19826,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>107046571</v>
+        <v>107045799</v>
       </c>
       <c r="B194" t="n">
         <v>79327</v>
@@ -19843,10 +19862,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>369117</v>
+        <v>369339</v>
       </c>
       <c r="R194" t="n">
-        <v>6938498</v>
+        <v>6938367</v>
       </c>
       <c r="S194" t="n">
         <v>25</v>
@@ -19905,7 +19924,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>107046697</v>
+        <v>107046571</v>
       </c>
       <c r="B195" t="n">
         <v>79327</v>
@@ -19941,10 +19960,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>369036</v>
+        <v>369117</v>
       </c>
       <c r="R195" t="n">
-        <v>6938510</v>
+        <v>6938498</v>
       </c>
       <c r="S195" t="n">
         <v>25</v>
@@ -20003,7 +20022,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>107046743</v>
+        <v>107046697</v>
       </c>
       <c r="B196" t="n">
         <v>79327</v>
@@ -20039,10 +20058,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>369033</v>
+        <v>369036</v>
       </c>
       <c r="R196" t="n">
-        <v>6938503</v>
+        <v>6938510</v>
       </c>
       <c r="S196" t="n">
         <v>25</v>
@@ -20101,7 +20120,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>107046785</v>
+        <v>107046743</v>
       </c>
       <c r="B197" t="n">
         <v>79327</v>
@@ -20137,10 +20156,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>369024</v>
+        <v>369033</v>
       </c>
       <c r="R197" t="n">
-        <v>6938494</v>
+        <v>6938503</v>
       </c>
       <c r="S197" t="n">
         <v>25</v>
@@ -20199,7 +20218,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>107047130</v>
+        <v>107046785</v>
       </c>
       <c r="B198" t="n">
         <v>79327</v>
@@ -20235,10 +20254,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>368979</v>
+        <v>369024</v>
       </c>
       <c r="R198" t="n">
-        <v>6938501</v>
+        <v>6938494</v>
       </c>
       <c r="S198" t="n">
         <v>25</v>
@@ -20297,7 +20316,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>107047356</v>
+        <v>107047130</v>
       </c>
       <c r="B199" t="n">
         <v>79327</v>
@@ -20333,10 +20352,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>369055</v>
+        <v>368979</v>
       </c>
       <c r="R199" t="n">
-        <v>6938560</v>
+        <v>6938501</v>
       </c>
       <c r="S199" t="n">
         <v>25</v>
@@ -20395,7 +20414,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>107047624</v>
+        <v>107047356</v>
       </c>
       <c r="B200" t="n">
         <v>79327</v>
@@ -20431,10 +20450,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>369324</v>
+        <v>369055</v>
       </c>
       <c r="R200" t="n">
-        <v>6938463</v>
+        <v>6938560</v>
       </c>
       <c r="S200" t="n">
         <v>25</v>
@@ -20493,7 +20512,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>107047712</v>
+        <v>107047624</v>
       </c>
       <c r="B201" t="n">
         <v>79327</v>
@@ -20529,10 +20548,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>369316</v>
+        <v>369324</v>
       </c>
       <c r="R201" t="n">
-        <v>6938481</v>
+        <v>6938463</v>
       </c>
       <c r="S201" t="n">
         <v>25</v>
@@ -20591,7 +20610,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>107047725</v>
+        <v>107047712</v>
       </c>
       <c r="B202" t="n">
         <v>79327</v>
@@ -20627,10 +20646,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>369308</v>
+        <v>369316</v>
       </c>
       <c r="R202" t="n">
-        <v>6938492</v>
+        <v>6938481</v>
       </c>
       <c r="S202" t="n">
         <v>25</v>
@@ -20689,7 +20708,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>107047816</v>
+        <v>107047725</v>
       </c>
       <c r="B203" t="n">
         <v>79327</v>
@@ -20725,10 +20744,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>369275</v>
+        <v>369308</v>
       </c>
       <c r="R203" t="n">
-        <v>6938506</v>
+        <v>6938492</v>
       </c>
       <c r="S203" t="n">
         <v>25</v>
@@ -20787,7 +20806,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>107842938</v>
+        <v>107047816</v>
       </c>
       <c r="B204" t="n">
         <v>79327</v>
@@ -20823,10 +20842,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>368974</v>
+        <v>369275</v>
       </c>
       <c r="R204" t="n">
-        <v>6938499</v>
+        <v>6938506</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -20853,12 +20872,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -20885,7 +20904,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>108004314</v>
+        <v>107842938</v>
       </c>
       <c r="B205" t="n">
         <v>79327</v>
@@ -20913,11 +20932,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
@@ -20925,10 +20940,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>369095</v>
+        <v>368974</v>
       </c>
       <c r="R205" t="n">
-        <v>6938472</v>
+        <v>6938499</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -20955,22 +20970,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -20985,19 +20990,19 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>108004356</v>
+        <v>108004314</v>
       </c>
       <c r="B206" t="n">
         <v>79327</v>
@@ -21025,7 +21030,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
@@ -21033,10 +21042,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>369100</v>
+        <v>369095</v>
       </c>
       <c r="R206" t="n">
-        <v>6938468</v>
+        <v>6938472</v>
       </c>
       <c r="S206" t="n">
         <v>25</v>
@@ -21066,9 +21075,19 @@
           <t>2023-04-10</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -21083,19 +21102,19 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>108004994</v>
+        <v>108004356</v>
       </c>
       <c r="B207" t="n">
         <v>79327</v>
@@ -21123,11 +21142,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
@@ -21135,10 +21150,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>368979</v>
+        <v>369100</v>
       </c>
       <c r="R207" t="n">
-        <v>6938465</v>
+        <v>6938468</v>
       </c>
       <c r="S207" t="n">
         <v>25</v>
@@ -21168,19 +21183,9 @@
           <t>2023-04-10</t>
         </is>
       </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>16:47</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21195,19 +21200,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>108005650</v>
+        <v>108004994</v>
       </c>
       <c r="B208" t="n">
         <v>79327</v>
@@ -21235,7 +21240,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
@@ -21243,10 +21252,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>368959</v>
+        <v>368979</v>
       </c>
       <c r="R208" t="n">
-        <v>6938497</v>
+        <v>6938465</v>
       </c>
       <c r="S208" t="n">
         <v>25</v>
@@ -21276,9 +21285,19 @@
           <t>2023-04-10</t>
         </is>
       </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -21293,19 +21312,19 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>108006715</v>
+        <v>108005650</v>
       </c>
       <c r="B209" t="n">
         <v>79327</v>
@@ -21333,22 +21352,18 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>368885</v>
+        <v>368959</v>
       </c>
       <c r="R209" t="n">
-        <v>6938364</v>
+        <v>6938497</v>
       </c>
       <c r="S209" t="n">
         <v>25</v>
@@ -21378,19 +21393,9 @@
           <t>2023-04-10</t>
         </is>
       </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>17:20</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -21405,19 +21410,19 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>108006771</v>
+        <v>108006715</v>
       </c>
       <c r="B210" t="n">
         <v>79327</v>
@@ -21445,7 +21450,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
@@ -21453,10 +21462,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>368875</v>
+        <v>368885</v>
       </c>
       <c r="R210" t="n">
-        <v>6938350</v>
+        <v>6938364</v>
       </c>
       <c r="S210" t="n">
         <v>25</v>
@@ -21486,9 +21495,19 @@
           <t>2023-04-10</t>
         </is>
       </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -21503,19 +21522,19 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>108006908</v>
+        <v>108006771</v>
       </c>
       <c r="B211" t="n">
         <v>79327</v>
@@ -21551,10 +21570,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>368870</v>
+        <v>368875</v>
       </c>
       <c r="R211" t="n">
-        <v>6938316</v>
+        <v>6938350</v>
       </c>
       <c r="S211" t="n">
         <v>25</v>
@@ -21613,7 +21632,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>108006982</v>
+        <v>108006908</v>
       </c>
       <c r="B212" t="n">
         <v>79327</v>
@@ -21641,11 +21660,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
@@ -21653,10 +21668,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>368881</v>
+        <v>368870</v>
       </c>
       <c r="R212" t="n">
-        <v>6938333</v>
+        <v>6938316</v>
       </c>
       <c r="S212" t="n">
         <v>25</v>
@@ -21686,19 +21701,9 @@
           <t>2023-04-10</t>
         </is>
       </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>17:25</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -21713,19 +21718,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>108007126</v>
+        <v>108006982</v>
       </c>
       <c r="B213" t="n">
         <v>79327</v>
@@ -21755,7 +21760,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -21765,10 +21770,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>368875</v>
+        <v>368881</v>
       </c>
       <c r="R213" t="n">
-        <v>6938311</v>
+        <v>6938333</v>
       </c>
       <c r="S213" t="n">
         <v>25</v>
@@ -21800,7 +21805,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -21810,7 +21815,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -21837,7 +21842,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>110456613</v>
+        <v>108007126</v>
       </c>
       <c r="B214" t="n">
         <v>79327</v>
@@ -21865,21 +21870,25 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>369659</v>
+        <v>368875</v>
       </c>
       <c r="R214" t="n">
-        <v>6938260</v>
+        <v>6938311</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -21903,12 +21912,22 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -21923,61 +21942,61 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>96506928</v>
+        <v>110456613</v>
       </c>
       <c r="B215" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>369574</v>
+        <v>369659</v>
       </c>
       <c r="R215" t="n">
-        <v>6938217</v>
+        <v>6938260</v>
       </c>
       <c r="S215" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -22001,12 +22020,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -22033,7 +22052,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>97690451</v>
+        <v>96506928</v>
       </c>
       <c r="B216" t="n">
         <v>83307</v>
@@ -22065,14 +22084,14 @@
       <c r="K216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>369171</v>
+        <v>369574</v>
       </c>
       <c r="R216" t="n">
-        <v>6938421</v>
+        <v>6938217</v>
       </c>
       <c r="S216" t="n">
         <v>25</v>
@@ -22099,12 +22118,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -22131,7 +22150,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>97690588</v>
+        <v>97690451</v>
       </c>
       <c r="B217" t="n">
         <v>83307</v>
@@ -22167,10 +22186,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>369149</v>
+        <v>369171</v>
       </c>
       <c r="R217" t="n">
-        <v>6938334</v>
+        <v>6938421</v>
       </c>
       <c r="S217" t="n">
         <v>25</v>
@@ -22229,7 +22248,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>97691007</v>
+        <v>97690588</v>
       </c>
       <c r="B218" t="n">
         <v>83307</v>
@@ -22265,10 +22284,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>369171</v>
+        <v>369149</v>
       </c>
       <c r="R218" t="n">
-        <v>6938294</v>
+        <v>6938334</v>
       </c>
       <c r="S218" t="n">
         <v>25</v>
@@ -22327,7 +22346,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>103557176</v>
+        <v>97691007</v>
       </c>
       <c r="B219" t="n">
         <v>83307</v>
@@ -22363,10 +22382,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>368850</v>
+        <v>369171</v>
       </c>
       <c r="R219" t="n">
-        <v>6938303</v>
+        <v>6938294</v>
       </c>
       <c r="S219" t="n">
         <v>25</v>
@@ -22393,12 +22412,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -22425,7 +22444,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>103565325</v>
+        <v>103557176</v>
       </c>
       <c r="B220" t="n">
         <v>83307</v>
@@ -22457,14 +22476,14 @@
       <c r="K220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>369329</v>
+        <v>368850</v>
       </c>
       <c r="R220" t="n">
-        <v>6938369</v>
+        <v>6938303</v>
       </c>
       <c r="S220" t="n">
         <v>25</v>
@@ -22491,12 +22510,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -22523,7 +22542,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>103565631</v>
+        <v>103565325</v>
       </c>
       <c r="B221" t="n">
         <v>83307</v>
@@ -22555,14 +22574,14 @@
       <c r="K221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>369190</v>
+        <v>369329</v>
       </c>
       <c r="R221" t="n">
-        <v>6938443</v>
+        <v>6938369</v>
       </c>
       <c r="S221" t="n">
         <v>25</v>
@@ -22621,7 +22640,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>103565997</v>
+        <v>103565631</v>
       </c>
       <c r="B222" t="n">
         <v>83307</v>
@@ -22657,10 +22676,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>368961</v>
+        <v>369190</v>
       </c>
       <c r="R222" t="n">
-        <v>6938418</v>
+        <v>6938443</v>
       </c>
       <c r="S222" t="n">
         <v>25</v>
@@ -22719,7 +22738,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>103568512</v>
+        <v>103565997</v>
       </c>
       <c r="B223" t="n">
         <v>83307</v>
@@ -22755,10 +22774,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>368996</v>
+        <v>368961</v>
       </c>
       <c r="R223" t="n">
-        <v>6938638</v>
+        <v>6938418</v>
       </c>
       <c r="S223" t="n">
         <v>25</v>
@@ -22817,7 +22836,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>103568537</v>
+        <v>103568512</v>
       </c>
       <c r="B224" t="n">
         <v>83307</v>
@@ -22849,14 +22868,14 @@
       <c r="K224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>368976</v>
+        <v>368996</v>
       </c>
       <c r="R224" t="n">
-        <v>6938665</v>
+        <v>6938638</v>
       </c>
       <c r="S224" t="n">
         <v>25</v>
@@ -22915,7 +22934,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>103568680</v>
+        <v>103568537</v>
       </c>
       <c r="B225" t="n">
         <v>83307</v>
@@ -22951,10 +22970,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>369085</v>
+        <v>368976</v>
       </c>
       <c r="R225" t="n">
-        <v>6938658</v>
+        <v>6938665</v>
       </c>
       <c r="S225" t="n">
         <v>25</v>
@@ -23013,7 +23032,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>103581869</v>
+        <v>103568680</v>
       </c>
       <c r="B226" t="n">
         <v>83307</v>
@@ -23049,10 +23068,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>369549</v>
+        <v>369085</v>
       </c>
       <c r="R226" t="n">
-        <v>6938234</v>
+        <v>6938658</v>
       </c>
       <c r="S226" t="n">
         <v>25</v>
@@ -23079,12 +23098,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -23111,7 +23130,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>103581918</v>
+        <v>103581869</v>
       </c>
       <c r="B227" t="n">
         <v>83307</v>
@@ -23143,14 +23162,14 @@
       <c r="K227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>369614</v>
+        <v>369549</v>
       </c>
       <c r="R227" t="n">
-        <v>6938215</v>
+        <v>6938234</v>
       </c>
       <c r="S227" t="n">
         <v>25</v>
@@ -23209,7 +23228,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>103583934</v>
+        <v>103581918</v>
       </c>
       <c r="B228" t="n">
         <v>83307</v>
@@ -23245,10 +23264,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>369061</v>
+        <v>369614</v>
       </c>
       <c r="R228" t="n">
-        <v>6938242</v>
+        <v>6938215</v>
       </c>
       <c r="S228" t="n">
         <v>25</v>
@@ -23307,7 +23326,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>103584228</v>
+        <v>103583934</v>
       </c>
       <c r="B229" t="n">
         <v>83307</v>
@@ -23343,10 +23362,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>369017</v>
+        <v>369061</v>
       </c>
       <c r="R229" t="n">
-        <v>6938332</v>
+        <v>6938242</v>
       </c>
       <c r="S229" t="n">
         <v>25</v>
@@ -23405,7 +23424,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>103585487</v>
+        <v>103584228</v>
       </c>
       <c r="B230" t="n">
         <v>83307</v>
@@ -23441,10 +23460,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>368900</v>
+        <v>369017</v>
       </c>
       <c r="R230" t="n">
-        <v>6938283</v>
+        <v>6938332</v>
       </c>
       <c r="S230" t="n">
         <v>25</v>
@@ -23503,7 +23522,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>107032918</v>
+        <v>103585487</v>
       </c>
       <c r="B231" t="n">
         <v>83307</v>
@@ -23535,14 +23554,14 @@
       <c r="K231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>368903</v>
+        <v>368900</v>
       </c>
       <c r="R231" t="n">
-        <v>6938218</v>
+        <v>6938283</v>
       </c>
       <c r="S231" t="n">
         <v>25</v>
@@ -23569,12 +23588,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -23601,7 +23620,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>107033444</v>
+        <v>107032918</v>
       </c>
       <c r="B232" t="n">
         <v>83307</v>
@@ -23637,10 +23656,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>369072</v>
+        <v>368903</v>
       </c>
       <c r="R232" t="n">
-        <v>6938256</v>
+        <v>6938218</v>
       </c>
       <c r="S232" t="n">
         <v>25</v>
@@ -23699,7 +23718,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>107033554</v>
+        <v>107033444</v>
       </c>
       <c r="B233" t="n">
         <v>83307</v>
@@ -23735,10 +23754,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>368971</v>
+        <v>369072</v>
       </c>
       <c r="R233" t="n">
-        <v>6938278</v>
+        <v>6938256</v>
       </c>
       <c r="S233" t="n">
         <v>25</v>
@@ -23797,7 +23816,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>107045032</v>
+        <v>107033554</v>
       </c>
       <c r="B234" t="n">
         <v>83307</v>
@@ -23829,14 +23848,14 @@
       <c r="K234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Ytteränget, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>369464</v>
+        <v>368971</v>
       </c>
       <c r="R234" t="n">
-        <v>6938309</v>
+        <v>6938278</v>
       </c>
       <c r="S234" t="n">
         <v>25</v>
@@ -23863,12 +23882,12 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -23895,7 +23914,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>107045167</v>
+        <v>107045032</v>
       </c>
       <c r="B235" t="n">
         <v>83307</v>
@@ -23931,10 +23950,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>369433</v>
+        <v>369464</v>
       </c>
       <c r="R235" t="n">
-        <v>6938296</v>
+        <v>6938309</v>
       </c>
       <c r="S235" t="n">
         <v>25</v>
@@ -23993,7 +24012,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>107045248</v>
+        <v>107045167</v>
       </c>
       <c r="B236" t="n">
         <v>83307</v>
@@ -24029,10 +24048,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>369401</v>
+        <v>369433</v>
       </c>
       <c r="R236" t="n">
-        <v>6938304</v>
+        <v>6938296</v>
       </c>
       <c r="S236" t="n">
         <v>25</v>
@@ -24091,7 +24110,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>107045331</v>
+        <v>107045248</v>
       </c>
       <c r="B237" t="n">
         <v>83307</v>
@@ -24127,10 +24146,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>369388</v>
+        <v>369401</v>
       </c>
       <c r="R237" t="n">
-        <v>6938335</v>
+        <v>6938304</v>
       </c>
       <c r="S237" t="n">
         <v>25</v>
@@ -24189,7 +24208,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>107045388</v>
+        <v>107045331</v>
       </c>
       <c r="B238" t="n">
         <v>83307</v>
@@ -24225,10 +24244,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>369416</v>
+        <v>369388</v>
       </c>
       <c r="R238" t="n">
-        <v>6938346</v>
+        <v>6938335</v>
       </c>
       <c r="S238" t="n">
         <v>25</v>
@@ -24287,7 +24306,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>107045556</v>
+        <v>107045388</v>
       </c>
       <c r="B239" t="n">
         <v>83307</v>
@@ -24323,10 +24342,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>369366</v>
+        <v>369416</v>
       </c>
       <c r="R239" t="n">
-        <v>6938332</v>
+        <v>6938346</v>
       </c>
       <c r="S239" t="n">
         <v>25</v>
@@ -24385,7 +24404,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>107045775</v>
+        <v>107045556</v>
       </c>
       <c r="B240" t="n">
         <v>83307</v>
@@ -24421,10 +24440,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>369364</v>
+        <v>369366</v>
       </c>
       <c r="R240" t="n">
-        <v>6938352</v>
+        <v>6938332</v>
       </c>
       <c r="S240" t="n">
         <v>25</v>
@@ -24483,7 +24502,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>107045848</v>
+        <v>107045775</v>
       </c>
       <c r="B241" t="n">
         <v>83307</v>
@@ -24519,10 +24538,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>369334</v>
+        <v>369364</v>
       </c>
       <c r="R241" t="n">
-        <v>6938371</v>
+        <v>6938352</v>
       </c>
       <c r="S241" t="n">
         <v>25</v>
@@ -24581,7 +24600,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>107046073</v>
+        <v>107045848</v>
       </c>
       <c r="B242" t="n">
         <v>83307</v>
@@ -24617,10 +24636,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>369320</v>
+        <v>369334</v>
       </c>
       <c r="R242" t="n">
-        <v>6938390</v>
+        <v>6938371</v>
       </c>
       <c r="S242" t="n">
         <v>25</v>
@@ -24679,7 +24698,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>107046194</v>
+        <v>107046073</v>
       </c>
       <c r="B243" t="n">
         <v>83307</v>
@@ -24715,10 +24734,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>369305</v>
+        <v>369320</v>
       </c>
       <c r="R243" t="n">
-        <v>6938393</v>
+        <v>6938390</v>
       </c>
       <c r="S243" t="n">
         <v>25</v>
@@ -24777,7 +24796,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>107046237</v>
+        <v>107046194</v>
       </c>
       <c r="B244" t="n">
         <v>83307</v>
@@ -24813,10 +24832,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>369294</v>
+        <v>369305</v>
       </c>
       <c r="R244" t="n">
-        <v>6938382</v>
+        <v>6938393</v>
       </c>
       <c r="S244" t="n">
         <v>25</v>
@@ -24875,7 +24894,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>107046263</v>
+        <v>107046237</v>
       </c>
       <c r="B245" t="n">
         <v>83307</v>
@@ -24911,10 +24930,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>369266</v>
+        <v>369294</v>
       </c>
       <c r="R245" t="n">
-        <v>6938402</v>
+        <v>6938382</v>
       </c>
       <c r="S245" t="n">
         <v>25</v>
@@ -24973,7 +24992,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>107046331</v>
+        <v>107046263</v>
       </c>
       <c r="B246" t="n">
         <v>83307</v>
@@ -25009,10 +25028,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>369227</v>
+        <v>369266</v>
       </c>
       <c r="R246" t="n">
-        <v>6938406</v>
+        <v>6938402</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -25071,7 +25090,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>107046404</v>
+        <v>107046331</v>
       </c>
       <c r="B247" t="n">
         <v>83307</v>
@@ -25107,10 +25126,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>369213</v>
+        <v>369227</v>
       </c>
       <c r="R247" t="n">
-        <v>6938418</v>
+        <v>6938406</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -25169,7 +25188,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>107046467</v>
+        <v>107046404</v>
       </c>
       <c r="B248" t="n">
         <v>83307</v>
@@ -25205,10 +25224,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>369192</v>
+        <v>369213</v>
       </c>
       <c r="R248" t="n">
-        <v>6938458</v>
+        <v>6938418</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -25267,7 +25286,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>107046518</v>
+        <v>107046467</v>
       </c>
       <c r="B249" t="n">
         <v>83307</v>
@@ -25303,10 +25322,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>369162</v>
+        <v>369192</v>
       </c>
       <c r="R249" t="n">
-        <v>6938457</v>
+        <v>6938458</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -25365,7 +25384,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>107046611</v>
+        <v>107046518</v>
       </c>
       <c r="B250" t="n">
         <v>83307</v>
@@ -25401,10 +25420,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>369107</v>
+        <v>369162</v>
       </c>
       <c r="R250" t="n">
-        <v>6938508</v>
+        <v>6938457</v>
       </c>
       <c r="S250" t="n">
         <v>25</v>
@@ -25463,7 +25482,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>107046648</v>
+        <v>107046611</v>
       </c>
       <c r="B251" t="n">
         <v>83307</v>
@@ -25499,10 +25518,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>369067</v>
+        <v>369107</v>
       </c>
       <c r="R251" t="n">
-        <v>6938505</v>
+        <v>6938508</v>
       </c>
       <c r="S251" t="n">
         <v>25</v>
@@ -25561,7 +25580,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>107046897</v>
+        <v>107046648</v>
       </c>
       <c r="B252" t="n">
         <v>83307</v>
@@ -25597,10 +25616,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>369010</v>
+        <v>369067</v>
       </c>
       <c r="R252" t="n">
-        <v>6938457</v>
+        <v>6938505</v>
       </c>
       <c r="S252" t="n">
         <v>25</v>
@@ -25659,7 +25678,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>107047087</v>
+        <v>107046897</v>
       </c>
       <c r="B253" t="n">
         <v>83307</v>
@@ -25695,10 +25714,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>368997</v>
+        <v>369010</v>
       </c>
       <c r="R253" t="n">
-        <v>6938473</v>
+        <v>6938457</v>
       </c>
       <c r="S253" t="n">
         <v>25</v>
@@ -25757,7 +25776,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>107047276</v>
+        <v>107047087</v>
       </c>
       <c r="B254" t="n">
         <v>83307</v>
@@ -25793,10 +25812,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>368986</v>
+        <v>368997</v>
       </c>
       <c r="R254" t="n">
-        <v>6938505</v>
+        <v>6938473</v>
       </c>
       <c r="S254" t="n">
         <v>25</v>
@@ -25855,7 +25874,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>107047326</v>
+        <v>107047276</v>
       </c>
       <c r="B255" t="n">
         <v>83307</v>
@@ -25891,10 +25910,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>369033</v>
+        <v>368986</v>
       </c>
       <c r="R255" t="n">
-        <v>6938568</v>
+        <v>6938505</v>
       </c>
       <c r="S255" t="n">
         <v>25</v>
@@ -25953,7 +25972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>107047370</v>
+        <v>107047326</v>
       </c>
       <c r="B256" t="n">
         <v>83307</v>
@@ -25989,10 +26008,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>369077</v>
+        <v>369033</v>
       </c>
       <c r="R256" t="n">
-        <v>6938552</v>
+        <v>6938568</v>
       </c>
       <c r="S256" t="n">
         <v>25</v>
@@ -26051,7 +26070,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>107047465</v>
+        <v>107047370</v>
       </c>
       <c r="B257" t="n">
         <v>83307</v>
@@ -26087,10 +26106,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>369060</v>
+        <v>369077</v>
       </c>
       <c r="R257" t="n">
-        <v>6938569</v>
+        <v>6938552</v>
       </c>
       <c r="S257" t="n">
         <v>25</v>
@@ -26149,7 +26168,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>107047578</v>
+        <v>107047465</v>
       </c>
       <c r="B258" t="n">
         <v>83307</v>
@@ -26185,10 +26204,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>369255</v>
+        <v>369060</v>
       </c>
       <c r="R258" t="n">
-        <v>6938509</v>
+        <v>6938569</v>
       </c>
       <c r="S258" t="n">
         <v>25</v>
@@ -26247,7 +26266,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>107047671</v>
+        <v>107047578</v>
       </c>
       <c r="B259" t="n">
         <v>83307</v>
@@ -26283,10 +26302,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>369331</v>
+        <v>369255</v>
       </c>
       <c r="R259" t="n">
-        <v>6938481</v>
+        <v>6938509</v>
       </c>
       <c r="S259" t="n">
         <v>25</v>
@@ -26345,7 +26364,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>107047806</v>
+        <v>107047671</v>
       </c>
       <c r="B260" t="n">
         <v>83307</v>
@@ -26381,10 +26400,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>369287</v>
+        <v>369331</v>
       </c>
       <c r="R260" t="n">
-        <v>6938531</v>
+        <v>6938481</v>
       </c>
       <c r="S260" t="n">
         <v>25</v>
@@ -26443,7 +26462,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>107047898</v>
+        <v>107047806</v>
       </c>
       <c r="B261" t="n">
         <v>83307</v>
@@ -26479,10 +26498,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>369275</v>
+        <v>369287</v>
       </c>
       <c r="R261" t="n">
-        <v>6938412</v>
+        <v>6938531</v>
       </c>
       <c r="S261" t="n">
         <v>25</v>
@@ -26541,7 +26560,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>108002738</v>
+        <v>107047898</v>
       </c>
       <c r="B262" t="n">
         <v>83307</v>
@@ -26577,10 +26596,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>369154</v>
+        <v>369275</v>
       </c>
       <c r="R262" t="n">
-        <v>6938423</v>
+        <v>6938412</v>
       </c>
       <c r="S262" t="n">
         <v>25</v>
@@ -26607,12 +26626,12 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -26639,7 +26658,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>108003496</v>
+        <v>108002738</v>
       </c>
       <c r="B263" t="n">
         <v>83307</v>
@@ -26675,10 +26694,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>369137</v>
+        <v>369154</v>
       </c>
       <c r="R263" t="n">
-        <v>6938429</v>
+        <v>6938423</v>
       </c>
       <c r="S263" t="n">
         <v>25</v>
@@ -26737,7 +26756,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>108004197</v>
+        <v>108003496</v>
       </c>
       <c r="B264" t="n">
         <v>83307</v>
@@ -26773,10 +26792,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>369089</v>
+        <v>369137</v>
       </c>
       <c r="R264" t="n">
-        <v>6938445</v>
+        <v>6938429</v>
       </c>
       <c r="S264" t="n">
         <v>25</v>
@@ -26806,19 +26825,9 @@
           <t>2023-04-10</t>
         </is>
       </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>16:31</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -26833,19 +26842,19 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>108004750</v>
+        <v>108004197</v>
       </c>
       <c r="B265" t="n">
         <v>83307</v>
@@ -26881,10 +26890,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>368994</v>
+        <v>369089</v>
       </c>
       <c r="R265" t="n">
-        <v>6938443</v>
+        <v>6938445</v>
       </c>
       <c r="S265" t="n">
         <v>25</v>
@@ -26914,9 +26923,19 @@
           <t>2023-04-10</t>
         </is>
       </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -26931,19 +26950,19 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>108005045</v>
+        <v>108004750</v>
       </c>
       <c r="B266" t="n">
         <v>83307</v>
@@ -26979,10 +26998,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>368983</v>
+        <v>368994</v>
       </c>
       <c r="R266" t="n">
-        <v>6938468</v>
+        <v>6938443</v>
       </c>
       <c r="S266" t="n">
         <v>25</v>
@@ -27012,19 +27031,9 @@
           <t>2023-04-10</t>
         </is>
       </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>16:49</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -27039,19 +27048,19 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>108007108</v>
+        <v>108005045</v>
       </c>
       <c r="B267" t="n">
         <v>83307</v>
@@ -27083,14 +27092,14 @@
       <c r="K267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>368873</v>
+        <v>368983</v>
       </c>
       <c r="R267" t="n">
-        <v>6938309</v>
+        <v>6938468</v>
       </c>
       <c r="S267" t="n">
         <v>25</v>
@@ -27122,7 +27131,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -27132,7 +27141,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -27159,7 +27168,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124625116</v>
+        <v>108007108</v>
       </c>
       <c r="B268" t="n">
         <v>83307</v>
@@ -27188,19 +27197,20 @@
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>368968</v>
+        <v>368873</v>
       </c>
       <c r="R268" t="n">
-        <v>6938352</v>
+        <v>6938309</v>
       </c>
       <c r="S268" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -27224,12 +27234,22 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -27244,66 +27264,60 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>107045888</v>
+        <v>124625116</v>
       </c>
       <c r="B269" t="n">
-        <v>57950</v>
+        <v>83307</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Ytteränget, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>369309</v>
+        <v>368968</v>
       </c>
       <c r="R269" t="n">
-        <v>6938358</v>
+        <v>6938352</v>
       </c>
       <c r="S269" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -27327,12 +27341,12 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -27359,7 +27373,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>107046035</v>
+        <v>107045888</v>
       </c>
       <c r="B270" t="n">
         <v>57950</v>
@@ -27400,10 +27414,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>369333</v>
+        <v>369309</v>
       </c>
       <c r="R270" t="n">
-        <v>6938482</v>
+        <v>6938358</v>
       </c>
       <c r="S270" t="n">
         <v>25</v>
@@ -27462,27 +27476,27 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>96508408</v>
+        <v>107046035</v>
       </c>
       <c r="B271" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -27492,22 +27506,21 @@
       </c>
       <c r="I271" t="inlineStr"/>
       <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>369472</v>
+        <v>369333</v>
       </c>
       <c r="R271" t="n">
-        <v>6938335</v>
+        <v>6938482</v>
       </c>
       <c r="S271" t="n">
         <v>25</v>
@@ -27534,12 +27547,12 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -27566,7 +27579,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>103557270</v>
+        <v>96508408</v>
       </c>
       <c r="B272" t="n">
         <v>57953</v>
@@ -27596,21 +27609,22 @@
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>368869</v>
+        <v>369472</v>
       </c>
       <c r="R272" t="n">
-        <v>6938302</v>
+        <v>6938335</v>
       </c>
       <c r="S272" t="n">
         <v>25</v>
@@ -27637,12 +27651,12 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -27669,7 +27683,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>103566533</v>
+        <v>103557270</v>
       </c>
       <c r="B273" t="n">
         <v>57953</v>
@@ -27710,10 +27724,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>368840</v>
+        <v>368869</v>
       </c>
       <c r="R273" t="n">
-        <v>6938243</v>
+        <v>6938302</v>
       </c>
       <c r="S273" t="n">
         <v>25</v>
@@ -27740,12 +27754,12 @@
       </c>
       <c r="Y273" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -27772,7 +27786,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>103568711</v>
+        <v>103566533</v>
       </c>
       <c r="B274" t="n">
         <v>57953</v>
@@ -27809,14 +27823,14 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>369124</v>
+        <v>368840</v>
       </c>
       <c r="R274" t="n">
-        <v>6938633</v>
+        <v>6938243</v>
       </c>
       <c r="S274" t="n">
         <v>25</v>
@@ -27875,7 +27889,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>103581875</v>
+        <v>103568711</v>
       </c>
       <c r="B275" t="n">
         <v>57953</v>
@@ -27916,10 +27930,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>369567</v>
+        <v>369124</v>
       </c>
       <c r="R275" t="n">
-        <v>6938227</v>
+        <v>6938633</v>
       </c>
       <c r="S275" t="n">
         <v>25</v>
@@ -27946,12 +27960,12 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -27978,7 +27992,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>103583786</v>
+        <v>103581875</v>
       </c>
       <c r="B276" t="n">
         <v>57953</v>
@@ -28010,19 +28024,19 @@
       <c r="K276" t="inlineStr"/>
       <c r="M276" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>368913</v>
+        <v>369567</v>
       </c>
       <c r="R276" t="n">
-        <v>6938243</v>
+        <v>6938227</v>
       </c>
       <c r="S276" t="n">
         <v>25</v>
@@ -28081,7 +28095,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>103583855</v>
+        <v>103583786</v>
       </c>
       <c r="B277" t="n">
         <v>57953</v>
@@ -28113,7 +28127,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
@@ -28122,10 +28136,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>369031</v>
+        <v>368913</v>
       </c>
       <c r="R277" t="n">
-        <v>6938279</v>
+        <v>6938243</v>
       </c>
       <c r="S277" t="n">
         <v>25</v>
@@ -28184,7 +28198,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>107045276</v>
+        <v>103583855</v>
       </c>
       <c r="B278" t="n">
         <v>57953</v>
@@ -28216,19 +28230,19 @@
       <c r="K278" t="inlineStr"/>
       <c r="M278" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Ytteränget, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>369416</v>
+        <v>369031</v>
       </c>
       <c r="R278" t="n">
-        <v>6938307</v>
+        <v>6938279</v>
       </c>
       <c r="S278" t="n">
         <v>25</v>
@@ -28255,12 +28269,12 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -28287,7 +28301,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>107045741</v>
+        <v>107045276</v>
       </c>
       <c r="B279" t="n">
         <v>57953</v>
@@ -28319,7 +28333,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="M279" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
@@ -28328,10 +28342,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>369349</v>
+        <v>369416</v>
       </c>
       <c r="R279" t="n">
-        <v>6938342</v>
+        <v>6938307</v>
       </c>
       <c r="S279" t="n">
         <v>25</v>
@@ -28390,7 +28404,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>107046950</v>
+        <v>107045741</v>
       </c>
       <c r="B280" t="n">
         <v>57953</v>
@@ -28422,7 +28436,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="M280" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P280" t="inlineStr">
@@ -28431,10 +28445,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>368995</v>
+        <v>369349</v>
       </c>
       <c r="R280" t="n">
-        <v>6938457</v>
+        <v>6938342</v>
       </c>
       <c r="S280" t="n">
         <v>25</v>
@@ -28493,7 +28507,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>107046968</v>
+        <v>107046950</v>
       </c>
       <c r="B281" t="n">
         <v>57953</v>
@@ -28525,7 +28539,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="M281" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
@@ -28534,10 +28548,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>369002</v>
+        <v>368995</v>
       </c>
       <c r="R281" t="n">
-        <v>6938474</v>
+        <v>6938457</v>
       </c>
       <c r="S281" t="n">
         <v>25</v>
@@ -28596,7 +28610,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>107047431</v>
+        <v>107046968</v>
       </c>
       <c r="B282" t="n">
         <v>57953</v>
@@ -28628,7 +28642,7 @@
       <c r="K282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
@@ -28637,10 +28651,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>369086</v>
+        <v>369002</v>
       </c>
       <c r="R282" t="n">
-        <v>6938588</v>
+        <v>6938474</v>
       </c>
       <c r="S282" t="n">
         <v>25</v>
@@ -28699,7 +28713,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>107842294</v>
+        <v>107047431</v>
       </c>
       <c r="B283" t="n">
         <v>57953</v>
@@ -28731,7 +28745,7 @@
       <c r="K283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
@@ -28740,10 +28754,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>369004</v>
+        <v>369086</v>
       </c>
       <c r="R283" t="n">
-        <v>6938506</v>
+        <v>6938588</v>
       </c>
       <c r="S283" t="n">
         <v>25</v>
@@ -28770,12 +28784,12 @@
       </c>
       <c r="Y283" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -28802,7 +28816,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>107843760</v>
+        <v>107842294</v>
       </c>
       <c r="B284" t="n">
         <v>57953</v>
@@ -28834,7 +28848,7 @@
       <c r="K284" t="inlineStr"/>
       <c r="M284" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
@@ -28843,10 +28857,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>369080</v>
+        <v>369004</v>
       </c>
       <c r="R284" t="n">
-        <v>6938473</v>
+        <v>6938506</v>
       </c>
       <c r="S284" t="n">
         <v>25</v>
@@ -28905,7 +28919,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>108004869</v>
+        <v>107843760</v>
       </c>
       <c r="B285" t="n">
         <v>57953</v>
@@ -28937,7 +28951,7 @@
       <c r="K285" t="inlineStr"/>
       <c r="M285" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
@@ -28946,10 +28960,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>368996</v>
+        <v>369080</v>
       </c>
       <c r="R285" t="n">
-        <v>6938464</v>
+        <v>6938473</v>
       </c>
       <c r="S285" t="n">
         <v>25</v>
@@ -28976,12 +28990,12 @@
       </c>
       <c r="Y285" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -29008,7 +29022,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>108005111</v>
+        <v>108004869</v>
       </c>
       <c r="B286" t="n">
         <v>57953</v>
@@ -29049,10 +29063,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>368958</v>
+        <v>368996</v>
       </c>
       <c r="R286" t="n">
-        <v>6938459</v>
+        <v>6938464</v>
       </c>
       <c r="S286" t="n">
         <v>25</v>
@@ -29111,7 +29125,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>108007420</v>
+        <v>108005111</v>
       </c>
       <c r="B287" t="n">
         <v>57953</v>
@@ -29148,14 +29162,14 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>368844</v>
+        <v>368958</v>
       </c>
       <c r="R287" t="n">
-        <v>6938214</v>
+        <v>6938459</v>
       </c>
       <c r="S287" t="n">
         <v>25</v>
@@ -29185,19 +29199,9 @@
           <t>2023-04-10</t>
         </is>
       </c>
-      <c r="Z287" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA287" t="inlineStr">
         <is>
           <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="AB287" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -29212,19 +29216,19 @@
       <c r="AT287" t="inlineStr"/>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>124624504</v>
+        <v>108007420</v>
       </c>
       <c r="B288" t="n">
         <v>57953</v>
@@ -29253,6 +29257,7 @@
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
+      <c r="K288" t="inlineStr"/>
       <c r="M288" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -29264,13 +29269,13 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>368934</v>
+        <v>368844</v>
       </c>
       <c r="R288" t="n">
-        <v>6938300</v>
+        <v>6938214</v>
       </c>
       <c r="S288" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -29294,12 +29299,22 @@
       </c>
       <c r="Y288" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -29314,19 +29329,19 @@
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>124626137</v>
+        <v>124624504</v>
       </c>
       <c r="B289" t="n">
         <v>57953</v>
@@ -29357,7 +29372,7 @@
       <c r="I289" t="inlineStr"/>
       <c r="M289" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
@@ -29366,13 +29381,13 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>368833</v>
+        <v>368934</v>
       </c>
       <c r="R289" t="n">
-        <v>6938244</v>
+        <v>6938300</v>
       </c>
       <c r="S289" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -29428,49 +29443,53 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>103583842</v>
+        <v>124626137</v>
       </c>
       <c r="B290" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>368960</v>
+        <v>368833</v>
       </c>
       <c r="R290" t="n">
-        <v>6938269</v>
+        <v>6938244</v>
       </c>
       <c r="S290" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -29494,12 +29513,12 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -29526,7 +29545,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>107843540</v>
+        <v>103583842</v>
       </c>
       <c r="B291" t="n">
         <v>57141</v>
@@ -29556,21 +29575,16 @@
       </c>
       <c r="I291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Ytteränget, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>368997</v>
+        <v>368960</v>
       </c>
       <c r="R291" t="n">
-        <v>6938450</v>
+        <v>6938269</v>
       </c>
       <c r="S291" t="n">
         <v>25</v>
@@ -29597,12 +29611,12 @@
       </c>
       <c r="Y291" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -29629,10 +29643,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>131327396</v>
+        <v>107843540</v>
       </c>
       <c r="B292" t="n">
-        <v>58592</v>
+        <v>57141</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -29640,45 +29654,43 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>102125</v>
+        <v>100138</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr"/>
       <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr"/>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P292" t="inlineStr">
         <is>
           <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>369418</v>
+        <v>368997</v>
       </c>
       <c r="R292" t="n">
-        <v>6938342</v>
+        <v>6938450</v>
       </c>
       <c r="S292" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
@@ -29702,22 +29714,12 @@
       </c>
       <c r="Y292" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="Z292" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB292" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -29732,39 +29734,39 @@
       <c r="AT292" t="inlineStr"/>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>Tobias Ljungquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>Tobias Ljungquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>131327393</v>
+        <v>131327396</v>
       </c>
       <c r="B293" t="n">
-        <v>57794</v>
+        <v>58592</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>102621</v>
+        <v>102125</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -29774,7 +29776,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -29822,7 +29824,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -29832,7 +29834,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -29859,10 +29861,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>131327395</v>
+        <v>131327393</v>
       </c>
       <c r="B294" t="n">
-        <v>58114</v>
+        <v>57794</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -29870,26 +29872,26 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>103021</v>
+        <v>102621</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -29937,7 +29939,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -29947,7 +29949,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -29974,10 +29976,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>103568881</v>
+        <v>131327395</v>
       </c>
       <c r="B295" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -29985,47 +29987,45 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Ytteränget, Härjedalen, Hjd</t>
+          <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>369259</v>
+        <v>369418</v>
       </c>
       <c r="R295" t="n">
-        <v>6938476</v>
+        <v>6938342</v>
       </c>
       <c r="S295" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -30049,12 +30049,22 @@
       </c>
       <c r="Y295" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -30069,19 +30079,19 @@
       <c r="AT295" t="inlineStr"/>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Tobias Ljungquist</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Tobias Ljungquist</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>131327394</v>
+        <v>103568881</v>
       </c>
       <c r="B296" t="n">
         <v>58057</v>
@@ -30111,26 +30121,28 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>Ytteränget, Hjd</t>
+          <t>Ytteränget, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>369418</v>
+        <v>369259</v>
       </c>
       <c r="R296" t="n">
-        <v>6938342</v>
+        <v>6938476</v>
       </c>
       <c r="S296" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -30154,22 +30166,12 @@
       </c>
       <c r="Y296" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="Z296" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB296" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -30184,22 +30186,22 @@
       <c r="AT296" t="inlineStr"/>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Tobias Ljungquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>Tobias Ljungquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>120352070</v>
+        <v>131327394</v>
       </c>
       <c r="B297" t="n">
-        <v>42865</v>
+        <v>58057</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -30207,46 +30209,45 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>216248</v>
+        <v>103031</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Baltiskt skogsfly</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Xestia baltica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Valle, 1940)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr"/>
       <c r="N297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
         <is>
-          <t>Linvallen, Hjd</t>
+          <t>Ytteränget, Hjd</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>369549</v>
+        <v>369418</v>
       </c>
       <c r="R297" t="n">
-        <v>6938214</v>
+        <v>6938342</v>
       </c>
       <c r="S297" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
@@ -30270,12 +30271,22 @@
       </c>
       <c r="Y297" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -30284,68 +30295,75 @@
       <c r="AE297" t="b">
         <v>0</v>
       </c>
-      <c r="AF297" t="inlineStr"/>
       <c r="AG297" t="b">
         <v>0</v>
       </c>
       <c r="AT297" t="inlineStr"/>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Tobias Ljungquist</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Tobias Ljungquist</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>103583751</v>
+        <v>120352070</v>
       </c>
       <c r="B298" t="n">
-        <v>106229</v>
+        <v>42865</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>221725</v>
+        <v>216248</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Baltiskt skogsfly</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Xestia baltica</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr"/>
+          <t>(Valle, 1940)</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Linvallen, Hjd</t>
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>368879</v>
+        <v>369549</v>
       </c>
       <c r="R298" t="n">
-        <v>6938246</v>
+        <v>6938214</v>
       </c>
       <c r="S298" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -30369,12 +30387,12 @@
       </c>
       <c r="Y298" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -30383,6 +30401,7 @@
       <c r="AE298" t="b">
         <v>0</v>
       </c>
+      <c r="AF298" t="inlineStr"/>
       <c r="AG298" t="b">
         <v>0</v>
       </c>
@@ -30401,7 +30420,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>103583787</v>
+        <v>103583751</v>
       </c>
       <c r="B299" t="n">
         <v>106229</v>
@@ -30437,10 +30456,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>368913</v>
+        <v>368879</v>
       </c>
       <c r="R299" t="n">
-        <v>6938243</v>
+        <v>6938246</v>
       </c>
       <c r="S299" t="n">
         <v>25</v>
@@ -30499,10 +30518,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>103583791</v>
+        <v>103583787</v>
       </c>
       <c r="B300" t="n">
-        <v>97983</v>
+        <v>106229</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -30510,21 +30529,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -30535,10 +30554,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>368938</v>
+        <v>368913</v>
       </c>
       <c r="R300" t="n">
-        <v>6938254</v>
+        <v>6938243</v>
       </c>
       <c r="S300" t="n">
         <v>25</v>
@@ -30594,6 +30613,104 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>103583791</v>
+      </c>
+      <c r="B301" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q301" t="n">
+        <v>368938</v>
+      </c>
+      <c r="R301" t="n">
+        <v>6938254</v>
+      </c>
+      <c r="S301" t="n">
+        <v>25</v>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AD301" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE301" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG301" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT301" t="inlineStr"/>
+      <c r="AW301" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX301" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY301" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34896-2022 artfynd.xlsx
+++ b/artfynd/A 34896-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY301"/>
+  <dimension ref="A1:AZ301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96506484</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507894</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045266</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046233</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110456774</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96506767</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1374,6 +1409,11 @@
           <t>Härjedalens kärlväxtflora 1994</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56732438</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556914</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557130</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1668,6 +1718,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107031956</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033380</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1863,6 +1923,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124622321</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045154</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2059,6 +2129,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556865</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557237</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2255,6 +2335,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103582073</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2353,6 +2438,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583919</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2451,6 +2541,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032342</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2548,6 +2643,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124622308</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2645,6 +2745,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124623267</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2743,6 +2848,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507255</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2873,6 +2983,11 @@
           <t>Svenska tryffelprojektet</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122005407</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2971,6 +3086,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103585484</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3069,6 +3189,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045050</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3167,6 +3292,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007472</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3279,6 +3409,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007510</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3377,6 +3512,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108008185</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3475,6 +3615,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103582287</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3573,6 +3718,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96505436</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3671,6 +3821,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507467</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3769,6 +3924,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103565379</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3867,6 +4027,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568498</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3965,6 +4130,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103582206</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4063,6 +4233,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046935</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4160,6 +4335,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124624109</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4258,6 +4438,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583503</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4356,6 +4541,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103584120</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4454,6 +4644,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507078</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4552,6 +4747,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568492</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4650,6 +4850,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96504852</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4748,6 +4953,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568328</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4846,6 +5056,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96504854</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4944,6 +5159,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96505248</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5042,6 +5262,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96505811</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5140,6 +5365,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96506332</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5238,6 +5468,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96506895</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5336,6 +5571,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96506999</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5434,6 +5674,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507537</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5532,6 +5777,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556868</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5630,6 +5880,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103565802</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5728,6 +5983,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566573</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5826,6 +6086,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568390</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5924,6 +6189,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103582020</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6022,6 +6292,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103582551</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6120,6 +6395,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103582716</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6218,6 +6498,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103584062</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6316,6 +6601,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103584153</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6414,6 +6704,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103585541</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6512,6 +6807,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032267</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6610,6 +6910,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032384</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6708,6 +7013,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032737</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6806,6 +7116,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033174</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6904,6 +7219,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033259</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7002,6 +7322,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033389</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7100,6 +7425,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033511</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7198,6 +7528,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045102</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7296,6 +7631,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045305</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7408,6 +7748,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108002141</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7520,6 +7865,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108002997</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7618,6 +7968,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108003507</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7716,6 +8071,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108003827</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7824,6 +8184,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108005011</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7936,6 +8301,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108006998</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8044,6 +8414,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007994</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8152,6 +8527,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108092290</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8250,6 +8630,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108343818</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8348,6 +8733,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568460</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8446,6 +8836,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568309</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8543,6 +8938,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124625988</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8641,6 +9041,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507087</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8739,6 +9144,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96505244</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8837,6 +9247,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507218</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8935,6 +9350,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507325</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9033,6 +9453,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507527</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9131,6 +9556,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97690511</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9229,6 +9659,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97691012</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9327,6 +9762,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97691090</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9425,6 +9865,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557178</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9523,6 +9968,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568335</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9621,6 +10071,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568624</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9719,6 +10174,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568740</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9817,6 +10277,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568794</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9915,6 +10380,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103581862</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10013,6 +10483,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103582233</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10111,6 +10586,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103582617</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10209,6 +10689,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583287</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10307,6 +10792,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583342</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10405,6 +10895,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583495</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10503,6 +10998,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583508</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10601,6 +11101,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583698</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10699,6 +11204,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583729</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10797,6 +11307,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583833</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10895,6 +11410,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583847</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10993,6 +11513,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583875</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11091,6 +11616,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583929</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11189,6 +11719,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103584004</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11287,6 +11822,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103584077</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11385,6 +11925,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103584124</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11483,6 +12028,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103584200</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11581,6 +12131,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103584236</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11679,6 +12234,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103585490</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11777,6 +12337,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103585509</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11875,6 +12440,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103585633</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11973,6 +12543,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107031692</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12071,6 +12646,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107031793</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12169,6 +12749,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032434</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12267,6 +12852,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032475</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12365,6 +12955,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032510</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12463,6 +13058,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032582</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12561,6 +13161,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032657</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12659,6 +13264,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032741</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12757,6 +13367,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032765</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12855,6 +13470,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032923</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12953,6 +13573,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033002</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13051,6 +13676,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033053</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13149,6 +13779,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033119</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13247,6 +13882,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033175</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13345,6 +13985,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033280</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13443,6 +14088,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033386</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13541,6 +14191,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033401</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13639,6 +14294,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033415</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13737,6 +14397,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033467</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13835,6 +14500,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033524</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13933,6 +14603,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045001</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14031,6 +14706,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045347</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14129,6 +14809,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045393</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14227,6 +14912,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045458</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14325,6 +15015,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045643</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14423,6 +15118,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045799</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14521,6 +15221,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046571</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14619,6 +15324,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046697</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14717,6 +15427,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046743</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14815,6 +15530,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046785</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14913,6 +15633,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047130</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15011,6 +15736,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047356</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15109,6 +15839,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047624</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15207,6 +15942,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047712</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15305,6 +16045,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047725</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15403,6 +16148,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047816</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15501,6 +16251,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107842938</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15613,6 +16368,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108004314</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15711,6 +16471,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108004356</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15823,6 +16588,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108004994</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15921,6 +16691,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108005650</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16033,6 +16808,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108006715</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16131,6 +16911,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108006771</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16229,6 +17014,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108006908</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16341,6 +17131,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108006982</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16453,6 +17248,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007126</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16565,6 +17365,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007346</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16673,6 +17478,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007968</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16771,6 +17581,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108008167</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16869,6 +17684,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108343819</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16967,6 +17787,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108344291</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17065,6 +17890,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110456613</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17163,6 +17993,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110456809</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17260,6 +18095,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124621864</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17358,6 +18198,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96506128</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17456,6 +18301,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96506601</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17554,6 +18404,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96506928</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17652,6 +18507,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507208</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17750,6 +18610,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507317</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17848,6 +18713,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507723</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17946,6 +18816,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97690451</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18044,6 +18919,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97690588</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18142,6 +19022,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97691007</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18240,6 +19125,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557176</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18338,6 +19228,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103565325</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18436,6 +19331,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103565631</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18534,6 +19434,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103565997</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18632,6 +19537,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568512</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18730,6 +19640,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568537</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18828,6 +19743,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568680</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18926,6 +19846,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103581869</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19024,6 +19949,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103581918</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19122,6 +20052,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583344</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19220,6 +20155,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583530</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19318,6 +20258,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583934</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19416,6 +20361,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103584023</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19514,6 +20464,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103584228</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19612,6 +20567,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103585487</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19710,6 +20670,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107031663</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19808,6 +20773,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107031776</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19906,6 +20876,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107031893</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20004,6 +20979,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107031930</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20102,6 +21082,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032113</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20200,6 +21185,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032413</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20298,6 +21288,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032545</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20396,6 +21391,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032918</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20494,6 +21494,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033115</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20592,6 +21597,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033377</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20690,6 +21700,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033444</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20788,6 +21803,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033554</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20886,6 +21906,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045032</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -20984,6 +22009,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045167</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21082,6 +22112,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045248</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21180,6 +22215,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045331</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21278,6 +22318,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045388</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21376,6 +22421,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045556</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21474,6 +22524,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045775</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21572,6 +22627,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045848</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21670,6 +22730,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046073</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21768,6 +22833,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046194</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21866,6 +22936,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046237</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -21964,6 +23039,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046263</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22062,6 +23142,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046331</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22160,6 +23245,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046404</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22258,6 +23348,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046467</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22356,6 +23451,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046518</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22454,6 +23554,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046611</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22552,6 +23657,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046648</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22650,6 +23760,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046897</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22748,6 +23863,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047087</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22846,6 +23966,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047276</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -22944,6 +24069,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047326</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23042,6 +24172,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047370</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23140,6 +24275,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047465</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23238,6 +24378,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047578</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23336,6 +24481,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047671</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23434,6 +24584,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047806</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23532,6 +24687,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047898</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23630,6 +24790,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108002738</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23728,6 +24893,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108003496</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23836,6 +25006,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108004197</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -23934,6 +25109,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108004750</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24042,6 +25222,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108005045</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24150,6 +25335,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007108</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24258,6 +25448,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007858</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24366,6 +25561,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007981</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24464,6 +25664,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108008324</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24561,6 +25766,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124622093</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24658,6 +25868,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124625116</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24761,6 +25976,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045888</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -24864,6 +26084,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046035</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -24968,6 +26193,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96506683</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25072,6 +26302,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96507309</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25176,6 +26411,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96508408</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25279,6 +26519,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556794</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25382,6 +26627,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557270</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25485,6 +26735,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557632</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25588,6 +26843,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566533</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25691,6 +26951,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568711</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25794,6 +27059,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103581875</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -25897,6 +27167,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583275</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -26000,6 +27275,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583511</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -26103,6 +27383,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583677</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26206,6 +27491,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583786</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26309,6 +27599,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583855</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26419,6 +27714,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106461233</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26522,6 +27822,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107031572</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26625,6 +27930,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107031715</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26728,6 +28038,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107031737</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -26831,6 +28146,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032448</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -26934,6 +28254,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032516</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -27037,6 +28362,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032591</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27140,6 +28470,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033396</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27243,6 +28578,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107033764</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -27346,6 +28686,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045276</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27449,6 +28794,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107045741</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -27552,6 +28902,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046950</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -27655,6 +29010,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107046968</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -27758,6 +29118,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107047431</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -27861,6 +29226,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107842294</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -27964,6 +29334,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107843760</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -28067,6 +29442,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108004869</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -28170,6 +29550,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108005111</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -28283,6 +29668,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007420</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -28386,6 +29776,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108343699</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28489,6 +29884,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108344232</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -28592,6 +29992,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108380113</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -28694,6 +30099,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124622472</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -28796,6 +30206,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124623242</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -28898,6 +30313,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124624504</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -29000,6 +30420,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124626137</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -29120,6 +30545,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125696719</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -29237,6 +30667,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134473952</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -29335,6 +30770,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583842</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -29438,6 +30878,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107843540</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -29553,6 +30998,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327396</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -29668,6 +31118,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327393</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -29783,6 +31238,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327395</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -29890,6 +31350,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568881</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -29988,6 +31453,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103582817</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -30097,6 +31567,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108379968</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -30212,6 +31687,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327394</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -30319,6 +31799,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120352070</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -30417,6 +31902,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583751</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -30515,6 +32005,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583787</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -30613,6 +32108,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583791</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -30711,8 +32211,315 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556881</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>